--- a/data/exports/cdsco_approvals.xlsx
+++ b/data/exports/cdsco_approvals.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$P$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$P$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -481,9 +481,9 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="51" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 5 Ml Vial</t>
+          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 10 Ml Vial</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Insulin Glargine (R Dna Origin) 100.0000 Iu/Ml,M-Cresol 2.7000 Milligram (Mg)</t>
+          <t>Insulin Glargine (R-Dna) 100.0000 Iu,M-Cresol (As Preservative) 2.7000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
+          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With  Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 10 Ml Vial</t>
+          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 5 Ml Vial</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Insulin Glargine (R-Dna) 100.0000 Iu,M-Cresol (As Preservative) 2.7000 Milligram (Mg)</t>
+          <t>Insulin Glargine (R Dna Origin) 100.0000 Iu/Ml,M-Cresol 2.7000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With  Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
+          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -739,44 +739,56 @@
           <t>Not Available</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Active Immunization against Pertussis</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Biological E - Shameerpet</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>composition, dosage</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:53:41</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Biological E - Shameerpet</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>CDSCO</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01 01:00:53</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -786,7 +798,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Tegoprazan</t>
+          <t>Upadacitinib Extended Release Tablets 15mg/30mg/45mg</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -796,37 +808,37 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Upadacitinib 15.0000 Milligram (Mg)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>For The Treatment Of Adults With Moderately To Severely Active Ulcerative Colitis Who Have Had An Inadequate Response Or Intolerance To One Or More Tnf Blockers.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>AMI LIFESCIENCES PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -841,7 +853,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:48</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr"/>
@@ -851,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Upadacitinib Extended Release Tablets 15mg/30mg/45mg</t>
+          <t>Hepatitis B Bulk  (Thiomersal ? Free)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -866,27 +878,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Upadacitinib 15.0000 Milligram (Mg)</t>
+          <t>For Hep B Hepatitis B Vaccine (rDNA) BP (Adult) [Brand: BEVAC]: Each Dose of 1 mL contains Purified HBsAg 20 µg, Aluminium Hydroxide gel equivalent to Al 0.5 mg, Preservative: Thiomersal BP 0.05 mg. Recombinant HBs antigen produced in Pichia pastoris (Yeast). For Hep B Hepatitis B Vaccine (rDNA) BP (Paediatric) [Brand: BEVAC]: Each Dose of 0.5 mL contains Purified HBsAg 10 µg, Aluminium Hydroxide gel equivalent to Al 0.25 mg, Preservative: Thiomersal BP 0.025 mg. Recombinant HBs antigen produced in Pichia pastoris (Yeast).</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Adult: Each Dose of 1 mL. Paediatric: Each Dose of 0.5 mL.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adults With Moderately To Severely Active Ulcerative Colitis Who Have Had An Inadequate Response Or Intolerance To One Or More Tnf Blockers.</t>
+          <t>Active Immunization against infection caused by Hepatitis B.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Biological E - Shameerpet</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -894,11 +906,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -911,12 +919,24 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:54:01</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -926,7 +946,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Hepatitis B Bulk  (Thiomersal ? Free)</t>
+          <t>Hib Conjugate Bulk (Thiomersal ? Free)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -939,19 +959,19 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Puriöed Capsular Polysaccharide of Hib (PRP) covalently S linked to 20 to 36.7 µg of Tetanus Toxoid 11 µg .......................................................... +++ AI (as AIPO ) ≤ 1.25 mg 4 S .................................................................................................... Preservative: Thiomersal BP/ Ph.Eur 0.01% w/v S</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>0.5 mL</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Active Immunization against Diphtheria, Tetanus, Pertussis, Hepatitis B and Haemophilus inøuenzae type b diseases.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -959,16 +979,12 @@
           <t>Biological E - Shameerpet</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -981,22 +997,34 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:56</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
+          <t>2026-07-02 00:53:23</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Hib Conjugate Bulk (Thiomersal ? Free)</t>
+          <t>Tegoprazan</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1009,36 +1037,32 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7-[[(4S)-5,7-difluoro-3,4-dihydro-2H-chromen-4-yl] oxy]-N, N,2-trimethyl-3-H-benzimidazole-5-carboxamide</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50mg tablets, 100mg</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>GERD, peptic ulcers, H. pylori eradication</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Biological E - Shameerpet</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+          <t>AMI LIFESCIENCES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -1051,12 +1075,24 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:51</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:53:00</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1359,19 +1395,19 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>The 0.5 ml contains following: Diphtheria Toxoid ≥2 IU (NLT 2.5Lf) Tetanus Toxoid ≥ 20 IU (NLT 5Lf) Pertussis Toxoid (PT) ≥ 8 mcg Filamentous Haemagglutinin (FHA) ≥ 8 mcg Pertactin (PRN) ≥ 2.5 mcg Aluminium Hydroxide, Al+++ ≤ 1.25 mg Sodium chloride 4.5 mg Water for injection q.s. For a full list of excipients, see section 6.1.</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>A single 0.5 ml dose of the vaccine is recommended.</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Tripavac is indicated for active booster immunization against tetanus, diphtheria, and pertussis in individuals aged 4 to 65 years.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1379,16 +1415,12 @@
           <t>SERUM INSTITUTE OF INDIA PVT. LTD.</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -1401,22 +1433,34 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:04</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
+          <t>2026-07-02 00:54:49</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Acellular Pertussis Prn Antigen</t>
+          <t>Fosravuconazole</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1429,36 +1473,32 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Fosravuconazole</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>POWDER (25kg/25kg)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Antifungal</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SERUM INSTITUTE OF INDIA PVT. LTD.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+          <t>M/s METROCHEM API PVT LTD - UNIT-IV</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -1471,12 +1511,24 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:00</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:54:15</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>http://www.metroapi.com/assets/images/mail-signatures/Metrochem-Products-Brochure.pdf</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pharmacompass.com/pharma-services/api-manufacturing-services/metrochem-api-private-limited</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>http://www.metroapi.com/assets/images/mail-signatures/Metrochem-Products-Brochure.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1551,12 +1603,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fosravuconazole</t>
+          <t>Acellular Pertussis Prn Antigen</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1569,36 +1621,32 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The 0.5 ml contains following: Diphtheria Toxoid ≥2 IU (NLT 2.5Lf) Tetanus Toxoid ≥ 20 IU (NLT 5Lf) Pertussis Toxoid (PT) ≥ 8 mcg Filamentous Haemagglutinin (FHA) ≥ 8 mcg Pertactin (PRN) ≥ 2.5 mcg Aluminium Hydroxide, Al+++ ≤ 1.25 mg Sodium chloride 4.5 mg Water for injection q.s.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>A single 0.5 ml dose of the vaccine is recommended.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Tripavac is indicated for active booster immunization against tetanus, diphtheria, and pertussis in individuals aged 4 to 65 years.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>M/s METROCHEM API PVT LTD - UNIT-IV</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+          <t>SERUM INSTITUTE OF INDIA PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -1611,22 +1659,34 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:58</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:54:31</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Brentuximab Vedotin 50 Milligram (Mg)</t>
+          <t>Glimepiride Ip+Metformin Hydrochloride Ip (As Extended Release)+Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1641,22 +1701,22 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Brentuximab Vedotin 50.0000 Milligram (Mg),Citric Acid Monohydrate 2.1000 Milligram (Mg),Sodium Citrate Dihydrate 56.1000 Milligram (Mg),?,?-Trehalose Dihydrate 700.0000 Milligram (Mg),Polysorbate 80 2.0000 Milligram (Mg)</t>
+          <t>Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin 100.0000 Milligram (Mg),Glimepiride 1.0000 Milligram (Mg),Metformin Hydrochloride (As Extended Release) 1000.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>1. Previously Untreated Stage Iii Or Iv Classical Hodgkin Lymphoma (Chl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Stage Iii Or Iv Chl, In Combination With Doxorubicin, Vinblastine, And Dacarbazine.  Adcetris Is Indicated For Adult Patients With Previously Untreated Cd30+ Stage Iib With Risk Factors, Stage Iii Or Stage Iv Hl In Combination With Etoposide, Cyclophosphamide, Doxorubicin, Dacarbazine, Dexamethasone (Brecadd),2. Classical Hodgkin Lymphoma (Chl) Consolidation Adcetris Is Indicated For The Treatment Of Adult Patients With Chl At High Risk Of Relapse Or Progression As Post-Autologous Hematopoietic Stem Cell Transplantation (Auto-Hsct) Consolidation.,3. Relapsed Classical Hodgkin Lymphoma (Chl) Adcetris Is Indicated For The Treatment Of Adult Patients With Chl After Failure Of Auto-Hsct Or After Failure Of At Least Two Prior Multi-Agent Chemotherapy Regimens In Patients Who Are Not Auto-Hsct Candidates.,4. Previously Untreated Systemic Anaplastic Large Cell Lymphoma (Salcl) Or Other Cd30- Expressing Peripheral T-Cell Lymphomas (Ptcl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Salcl Or Other Cd30-Expressing Ptcl, Including Angioimmunoblastic T-Cell Lymphoma And Ptcl Not Otherwise Specified, In Combination With Cyclophosphamide, Doxorubicin, And Prednisone.,5. Relapsed Systemic Anaplastic Large Cell Lymphoma (Salcl) Adcetris Is Indicated For The Treatment Of Adult Patients With Salcl After Failure Of At Least One Prior Multi-Agent Chemotherapy Regimen.,6. Relapsed Primary Cutaneous Anaplastic Large Cell Lymphoma (Pcalcl) Or Cd30- Expressing Mycosis Fungoides (Mf) Adcetris Is Indicated For The Treatment Of Adult Patients With Pcalcl Or Cd30-Expressing Mf Who Have Received Prior Systemic Therapy.</t>
+          <t>For The Treatment Of Patients With Type Ii Diabetes Mellitus</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1696,7 +1756,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dapagliflozin+Metformin Hydrochloride Sr+Pioglitazone</t>
+          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin+Eplerenone</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1711,22 +1771,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Pioglitazone Hydrochloride 15.0000 Milligram (Mg),Metformin Hydrochloride Sr 1000.0000 Milligram (Mg)</t>
+          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin 10.0000 Milligram (Mg),Eplerenone 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Film coated tablet</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
+          <t>In Patients With Chronic Kidney Disease</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Limited</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1761,12 +1821,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Glimepiride Ip+Metformin Hydrochloride Ip (As Extended Release)+Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin</t>
+          <t>Semaglutide Injection</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1781,22 +1841,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin 100.0000 Milligram (Mg),Glimepiride 1.0000 Milligram (Mg),Metformin Hydrochloride (As Extended Release) 1000.0000 Milligram (Mg)</t>
+          <t>Semaglutide 0.6800 Mg/Ml (2mg/3ml)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Injection</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>For The Treatment Of Patients With Type Ii Diabetes Mellitus</t>
+          <t>Indicated For The Treatment Of Adults With Insufficiently Controlled Type 2 Diabetes Mellitus As An Adjunct To Diet And Exercise ? As Monotherapy, When Metformin Is Considered Inappropriate Due To Intolerance Or Contraindications. ? In Addition To Other Medicinal Products For The Treatment Of Diabetes.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
+          <t>Dr. Reddys Laboratories Limited</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1831,12 +1891,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin+Eplerenone</t>
+          <t>Brentuximab Vedotin 50 Milligram (Mg)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1851,22 +1911,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin 10.0000 Milligram (Mg),Eplerenone 25.0000 Milligram (Mg)</t>
+          <t>Brentuximab Vedotin 50.0000 Milligram (Mg),Citric Acid Monohydrate 2.1000 Milligram (Mg),Sodium Citrate Dihydrate 56.1000 Milligram (Mg),?,?-Trehalose Dihydrate 700.0000 Milligram (Mg),Polysorbate 80 2.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Film coated tablet</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>In Patients With Chronic Kidney Disease</t>
+          <t>1. Previously Untreated Stage Iii Or Iv Classical Hodgkin Lymphoma (Chl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Stage Iii Or Iv Chl, In Combination With Doxorubicin, Vinblastine, And Dacarbazine.  Adcetris Is Indicated For Adult Patients With Previously Untreated Cd30+ Stage Iib With Risk Factors, Stage Iii Or Stage Iv Hl In Combination With Etoposide, Cyclophosphamide, Doxorubicin, Dacarbazine, Dexamethasone (Brecadd),2. Classical Hodgkin Lymphoma (Chl) Consolidation Adcetris Is Indicated For The Treatment Of Adult Patients With Chl At High Risk Of Relapse Or Progression As Post-Autologous Hematopoietic Stem Cell Transplantation (Auto-Hsct) Consolidation.,3. Relapsed Classical Hodgkin Lymphoma (Chl) Adcetris Is Indicated For The Treatment Of Adult Patients With Chl After Failure Of Auto-Hsct Or After Failure Of At Least Two Prior Multi-Agent Chemotherapy Regimens In Patients Who Are Not Auto-Hsct Candidates.,4. Previously Untreated Systemic Anaplastic Large Cell Lymphoma (Salcl) Or Other Cd30- Expressing Peripheral T-Cell Lymphomas (Ptcl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Salcl Or Other Cd30-Expressing Ptcl, Including Angioimmunoblastic T-Cell Lymphoma And Ptcl Not Otherwise Specified, In Combination With Cyclophosphamide, Doxorubicin, And Prednisone.,5. Relapsed Systemic Anaplastic Large Cell Lymphoma (Salcl) Adcetris Is Indicated For The Treatment Of Adult Patients With Salcl After Failure Of At Least One Prior Multi-Agent Chemotherapy Regimen.,6. Relapsed Primary Cutaneous Anaplastic Large Cell Lymphoma (Pcalcl) Or Cd30- Expressing Mycosis Fungoides (Mf) Adcetris Is Indicated For The Treatment Of Adult Patients With Pcalcl Or Cd30-Expressing Mf Who Have Received Prior Systemic Therapy.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
+          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1901,12 +1961,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Semaglutide Injection</t>
+          <t>Dapagliflozin+Metformin Hydrochloride Sr+Pioglitazone</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1921,22 +1981,22 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Semaglutide 0.6800 Mg/Ml (2mg/3ml)</t>
+          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Pioglitazone Hydrochloride 15.0000 Milligram (Mg),Metformin Hydrochloride Sr 1000.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Indicated For The Treatment Of Adults With Insufficiently Controlled Type 2 Diabetes Mellitus As An Adjunct To Diet And Exercise ? As Monotherapy, When Metformin Is Considered Inappropriate Due To Intolerance Or Contraindications. ? In Addition To Other Medicinal Products For The Treatment Of Diabetes.</t>
+          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Dr. Reddys Laboratories Limited</t>
+          <t>Eris Lifesciences Limited</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -2186,7 +2246,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>L-Carnitine L-Tartrate</t>
+          <t>Ribociclib Succinate</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2199,36 +2259,32 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ribociclib succinate</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>600 mg once daily</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>early breast cancer or advanced or metastatic breast cancer</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Symbio Generics</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+          <t>Natco Pharma Limited</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -2241,12 +2297,24 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:06</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="inlineStr"/>
-      <c r="P25" s="4" t="inlineStr"/>
+          <t>2026-07-02 00:51:46</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.e-lactancia.org/media/papers/Ribociclib-DS-Novartis2023.pdf</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2017/209092s000lbl.pdf</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oncologynewscentral.com/drugs/monograph/173394-317022/ribociclib-oral</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2321,12 +2389,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Revefenacin Inhalation Solution. 175 Mcg /3ml</t>
+          <t>Levocarnitine I.P, U.S.P, E.P</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2336,37 +2404,37 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Revefenacin 175.0000 Mcg/3ml</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Inhalation solution</t>
+          <t>Adults: The recommended oral dosage for adults is 990 mg two or three times a day using the 330 mg tablets, depending on clinical response. Infants and children: The recommended oral dosage for infants and children is between 50 and 100 mg/kg/day in divided doses, with a maximum of 3 g/day. Dosage should begin at 50 mg/kg/day. The exact dosage will depend on clinical response.</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Indicated For The Maintenance Treatment Of  Patients With Chronic Obstructive Pulmonary Disease (Copd)</t>
+          <t>Levocarnitine is indicated in the treatment of primary systemic carnitine deficiency. In the reported cases, the clinical presentation consisted of recurrent episodes of Reye-like encephalopathy, hypoketotic hypoglycemia, and/or cardiomyopathy. Associated symptoms included hypotonia, muscle weakness and failure to thrive. A diagnosis of primary carnitine deficiency requires that serum, red cell and/or tissue carnitine levels be low and that the patient does not have a primary defect in fatty acid or organic acid oxidation (see CLINICAL PHARMACOLOGY). In some patients, particularly those presenting with cardiomyopathy, carnitine supplementation rapidly alleviated signs and symptoms. Treatment should include, in addition to carnitine, supportive and other therapy as indicated by [...] Levocarnitine is also indicated for acute and chronic treatment of patients with an inborn error of metabolism which results in a secondary carnitine deficiency.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>AKUMS DRUGS &amp; PHARMACEUTICALS LIMITED</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Symbio Generics</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2381,22 +2449,34 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="inlineStr"/>
-      <c r="P27" s="4" t="inlineStr"/>
+          <t>2026-07-02 00:51:33</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>https://...</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/fda/fdaDrugXsl.cfm?setid=c8a590a7-628b-45c5-ac2c-24214a69eaa6</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/fda/fdaDrugXsl.cfm?setid=c8a590a7-628b-45c5-ac2c-24214a69eaa6</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Esaxerenone Tablets 1.25 Mg, 2.5 Mg And 5 Mg</t>
+          <t>L-Carnitine L-Tartrate</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2406,37 +2486,37 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Esaxerenone 1.2500 Milligram (Mg)</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Tablets</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Indicated For The Treatment Of Hypertension</t>
+          <t>L-Carnitine-L-tartrate</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Sun Pharma Laboratories Limited</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Symbio Generics</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>dosage, indication</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2451,22 +2531,34 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:51:16</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chemspider.com/Chemical-Structure.22177977.html</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Levocarnitine I.P, U.S.P, E.P</t>
+          <t>Revefenacin Inhalation Solution. 175 Mcg /3ml</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2476,37 +2568,37 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Revefenacin 175.0000 Mcg/3ml</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Inhalation solution</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Indicated For The Maintenance Treatment Of  Patients With Chronic Obstructive Pulmonary Disease (Copd)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Symbio Generics</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>AKUMS DRUGS &amp; PHARMACEUTICALS LIMITED</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2521,7 +2613,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:09</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr"/>
@@ -2531,12 +2623,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Ribociclib Succinate</t>
+          <t>Esaxerenone Tablets 1.25 Mg, 2.5 Mg And 5 Mg</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2546,37 +2638,37 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Esaxerenone 1.2500 Milligram (Mg)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Indicated For The Treatment Of Hypertension</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Natco Pharma Limited</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Sun Pharma Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2591,7 +2683,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:14</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
@@ -2601,12 +2693,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Ketorolac Tromethamine Sublingual Tablets 30mg</t>
+          <t>Tetanus Vaccine (Adsorbed) I.P.- Ready To Fill Bulk (Rtfb)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2616,37 +2708,37 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Ketorolac Tromethamine 30.0000 Milligram (Mg)</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Sublingual Tablets</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>For The Treatment Of Migraine Headache In Adults Only</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Troikaa Pharmaceuticals Ltd</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>INDIAN IMMUNOLOGICAL LIMITED</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition, dosage, indication</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -2661,7 +2753,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
+          <t>2026-07-02 00:51:55</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr"/>
@@ -2676,7 +2768,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Relugolix Tablets 120mg</t>
+          <t>Ketorolac Tromethamine Sublingual Tablets 30mg</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2691,22 +2783,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Relugolix Tablets 120mg 120.0000 Milligram (Mg)</t>
+          <t>Ketorolac Tromethamine 30.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Sublingual Tablets</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adult Patients With Advance Prostate Cancer</t>
+          <t>For The Treatment Of Migraine Headache In Adults Only</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Troikaa Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2741,12 +2833,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Metformin Prolonged Release 500 Mg/1000 Mg Tablets Bp+Sitagliptin 50 Mg/50 Mg</t>
+          <t>Relugolix Tablets 120mg</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2761,7 +2853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Sitagliptin Phosphate Monohydrate 50.0000 Milligram (Mg),Metformin Hydrochloride 1000.0000 Milligram (Mg)</t>
+          <t>Relugolix Tablets 120mg 120.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2771,12 +2863,12 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus When Treatment With Both Sitagliptin And Metformin Is Appropriate.</t>
+          <t>For The Treatment Of Adult Patients With Advance Prostate Cancer</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Windlas Biotech Limited</t>
+          <t>Hetero Labs Limited</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2811,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Tetanus Vaccine (Adsorbed) I.P.- Ready To Fill Bulk (Rtfb)</t>
+          <t>Metformin Prolonged Release 500 Mg/1000 Mg Tablets Bp+Sitagliptin 50 Mg/50 Mg</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2826,37 +2918,37 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Sitagliptin Phosphate Monohydrate 50.0000 Milligram (Mg),Metformin Hydrochloride 1000.0000 Milligram (Mg)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>It Is Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus When Treatment With Both Sitagliptin And Metformin Is Appropriate.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>INDIAN IMMUNOLOGICAL LIMITED</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Windlas Biotech Limited</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2871,7 +2963,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:16</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
@@ -2951,12 +3043,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Semaglutide Injection 1mg/1.5ml (0.68mg/Ml), 2mg/1.5ml (1.34mg/Ml) , 4mg/3ml (1.34mg/Ml)  , 6.8mg/3ml (2.27mg/Ml), 9.6mg/3ml (3.2mg/Ml)</t>
+          <t>Gliclazide+Sitagliptin Phosphate Monohydrate</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2971,22 +3063,22 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Semaglutide 1.0000 Mg/1 Point 5</t>
+          <t>Sitagliptin Phosphate Monohydrate 100.0000 Milligram (Mg),Gliclazide 30.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of ? 30 Kg/M2 Or Greater (Obesity) Or ? 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
+          <t>Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus Inadequately Controlled With Metformin Monotherapy.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Eris Therapeutics Limited</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -3021,12 +3113,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Relugolix</t>
+          <t>Respiratory Syncytial Virus (Rsv) Vaccine (Recombinant, Adjuvanted)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3036,37 +3128,37 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Rsvpref3 Antigen 120.0000 Micrograms (?g),Trehalose Dihydrate 14.7000 Milligram (Mg),Polysorbate 80 (Ps80) 0.1800 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.2900 Milligram (Mg),Dipotassium Phosphate (K2hpo4) 0.2600 Milligram (Mg),3-O-Desacyl-4?- Monophosphoryl Lipid A (Mpl) 25.0000 Micrograms (?g),Purified Quillaja Saponin (Qs-21) 25.0000 Micrograms (?g),Dioleoyl Phosphatidylcholine (Dopc) 500.0000 Micrograms (?g),Cholesterol 125.0000 Micrograms (?g),Sodium Chloride (Nacl) 4.4000 Milligram (Mg),Disodium Phosphate Anhydrous (Na2hpo4) 0.1500 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.5400 Milligram (Mg),Water For Injection (Wfi) Q.S Ad 0.5000 Ml</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Powder and suspension for suspension for injection</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Arexvy Is Indicated For Active Immunisation For The Prevention Of Lower Respiratory Tract Disease (Lrtd) Caused By Respiratory Syncytial Virus In: ?	Adults 60 Years Of Age And Older; ?	Adults 50 Through 59 Years Of Age Who Are At Increased Risk For Rsv Disease.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>GLAXOSMITHKLINE PHARMACEUTICALS LIMITED</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -3081,7 +3173,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:20</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr"/>
@@ -3091,12 +3183,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Gliclazide+Sitagliptin Phosphate Monohydrate</t>
+          <t>Semaglutide Injection 1mg/1.5ml (0.68mg/Ml), 2mg/1.5ml (1.34mg/Ml) , 4mg/3ml (1.34mg/Ml)  , 6.8mg/3ml (2.27mg/Ml), 9.6mg/3ml (3.2mg/Ml)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3111,22 +3203,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sitagliptin Phosphate Monohydrate 100.0000 Milligram (Mg),Gliclazide 30.0000 Milligram (Mg)</t>
+          <t>Semaglutide 1.0000 Mg/1 Point 5</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Injection</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus Inadequately Controlled With Metformin Monotherapy.</t>
+          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of ? 30 Kg/M2 Or Greater (Obesity) Or ? 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Eris Therapeutics Limited</t>
+          <t>Hetero Labs Limited</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -3166,7 +3258,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Dapagliflozin+Metformin Hydrochloride (Sr)+Vildagliptin (Sr)</t>
+          <t>Chlorpheniramine Maleate Ip 2 Mg+Paracetamol Ip 500 Mg+Phenylephrine Hydrochloride Ip 10 Mg</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3181,7 +3273,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Metformin Hydrochloride 1000.0000 Milligram (Mg),Vildagliptin 100.0000 Milligram (Mg)</t>
+          <t>Paracetamol 500.0000 Milligram (Mg),Phenylephrine Hydrochloride 10.0000 Milligram (Mg),Chlorpheniramine Maleate 2.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3191,12 +3283,12 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>For The Treatment Of Patients With Type 2 Diabetes Mellitus</t>
+          <t>To Relieve The Symptoms Of Cold</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Eris Therapeutics Limited</t>
+          <t>CENTAUR PHARMACEUTICALS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -3236,7 +3328,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Chlorpheniramine Maleate Ip 2 Mg+Paracetamol Ip 500 Mg+Phenylephrine Hydrochloride Ip 10 Mg</t>
+          <t>Dapagliflozin+Metformin Hydrochloride (Sr)+Vildagliptin (Sr)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3251,7 +3343,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Paracetamol 500.0000 Milligram (Mg),Phenylephrine Hydrochloride 10.0000 Milligram (Mg),Chlorpheniramine Maleate 2.0000 Milligram (Mg)</t>
+          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Metformin Hydrochloride 1000.0000 Milligram (Mg),Vildagliptin 100.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3261,12 +3353,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>To Relieve The Symptoms Of Cold</t>
+          <t>For The Treatment Of Patients With Type 2 Diabetes Mellitus</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>CENTAUR PHARMACEUTICALS PRIVATE LIMITED</t>
+          <t>Eris Therapeutics Limited</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -3301,12 +3393,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Respiratory Syncytial Virus (Rsv) Vaccine (Recombinant, Adjuvanted)</t>
+          <t>Relugolix</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3316,37 +3408,37 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Rsvpref3 Antigen 120.0000 Micrograms (?g),Trehalose Dihydrate 14.7000 Milligram (Mg),Polysorbate 80 (Ps80) 0.1800 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.2900 Milligram (Mg),Dipotassium Phosphate (K2hpo4) 0.2600 Milligram (Mg),3-O-Desacyl-4?- Monophosphoryl Lipid A (Mpl) 25.0000 Micrograms (?g),Purified Quillaja Saponin (Qs-21) 25.0000 Micrograms (?g),Dioleoyl Phosphatidylcholine (Dopc) 500.0000 Micrograms (?g),Cholesterol 125.0000 Micrograms (?g),Sodium Chloride (Nacl) 4.4000 Milligram (Mg),Disodium Phosphate Anhydrous (Na2hpo4) 0.1500 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.5400 Milligram (Mg),Water For Injection (Wfi) Q.S Ad 0.5000 Ml</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Powder and suspension for suspension for injection</t>
+          <t>Initiate treatment of ORGOVYX with a loading dose of 360 mg on the first day and continue treatment with a 120 mg dose taken orally once daily at approximately the same time each day. ORGOVYX can be taken with or without food. Instruct patients to swallow tablets whole and not to crush or chew tablets. Advise patients to take a missed dose of ORGOVYX as soon as they remember. If the dose was missed by more than 12 hours, patients should not take the missed dose and resume with the next scheduled dose. If treatment with ORGOVYX is interrupted for greater than 7 days, restart ORGOVYX with a loading dose of 360 mg on the first day, and continue with a dose of 120 mg once daily.</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Arexvy Is Indicated For Active Immunisation For The Prevention Of Lower Respiratory Tract Disease (Lrtd) Caused By Respiratory Syncytial Virus In: ?	Adults 60 Years Of Age And Older; ?	Adults 50 Through 59 Years Of Age Who Are At Increased Risk For Rsv Disease.</t>
+          <t>treatment of adult patients with advanced prostate cancer.</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>GLAXOSMITHKLINE PHARMACEUTICALS LIMITED</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -3361,12 +3453,24 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr"/>
-      <c r="O41" s="4" t="inlineStr"/>
-      <c r="P41" s="4" t="inlineStr"/>
+          <t>2026-07-02 00:55:58</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>https://...</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2020/214621s000lbl.pdf</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.orgovyxhcp.com/dosing</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3641,7 +3745,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:11</t>
+          <t>2026-07-02 00:54:59</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr"/>
@@ -3711,12 +3815,24 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:07</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:56:21</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3866,7 +3982,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Tegoprazan</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3876,37 +3992,37 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Ferric Oxide Red Usp Nf 0.0000 Q.S.,Titanium Dioxide 0.0000 Q.S.,Excipients 0.0000 Q.S.,Ferric Oxide Black Usp Nf 0.0000 Q.S.,Tegoprazan 25.0000 Milligram (Mg)</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Film coated tablet</t>
+          <t>Adults—At first, 0.25 milligrams (mg) injected under the skin once a week for 4 weeks. Your doctor may increase your dose as needed.</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Tegoprazan Tablets 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease.,Tegoprazan Tablets 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non-Erosive Gastroesophageal Reflux Disease, Gastric Ulcer</t>
+          <t>Indicated for non-cirrhotic metabolic dysfunction-associated steatohepatitis (MASH) with moderate or advanced liver fibrosis (stage F2 or F3); as an adjunct to diet and exercise to improve glycemic control in adults with type 2 diabetes; and to reduce the risk of major adverse cardiovascular events in adults with type 2 diabetes and established cardiovascular disease.</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>M/s. VXL Life Sciences</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3921,12 +4037,20 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
+          <t>2026-07-02 00:56:37</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr"/>
-      <c r="O49" s="4" t="inlineStr"/>
-      <c r="P49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mayoclinic.org/drugs-supplements/semaglutide-subcutaneous-route/description/drg-20406730</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semaglutide</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4001,12 +4125,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Semaglutide Injection</t>
+          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4021,22 +4145,22 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Semaglutide 0.2500 Milligram (Mg)</t>
+          <t>Filamentous Haemagglutinin 25.0000 Micrograms (?g),Tetanus Toxoid 40.0000 Iu,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 Du,Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 Du,Pertussis Toxoid 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 Du,Diphtheria Toxoid 30.0000 Iu</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Suspension for injection in a prefilled syringe</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of - ?	30 Kg/M2 Or Greater (Obesity) Or ?	27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
+          <t>"This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations"</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -4076,7 +4200,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
+          <t>Enfortumab Vedotin</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4091,22 +4215,22 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Filamentous Haemagglutinin 25.0000 Micrograms (?g),Tetanus Toxoid 40.0000 Iu,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 Du,Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 Du,Pertussis Toxoid 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 Du,Diphtheria Toxoid 30.0000 Iu</t>
+          <t>Enfortumab Vedotin, 20.0000 Milligram (Mg),Polysorbate 20, Nf, Jpe 0.4000 Milligram (Mg),Histidine Hydrochloride Monohydrate 4.6200 Milligram (Mg),Trehalose Dihydrate, Nf 110.0000 Milligram (Mg),Histidine 2.8000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Suspension for injection in a prefilled syringe</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>"This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations"</t>
+          <t>Padcev, In Combination With Pembrolizumab, Is Indicated For The Treatment Of Adult Patients With Locally Advanced Or Metastatic Urothelial Cancer (Muc).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+          <t>Astellas Pharma India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -4146,7 +4270,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Enfortumab Vedotin</t>
+          <t>Mirvetuximab Soravtansine Injection 5mg/Ml</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4161,22 +4285,22 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Enfortumab Vedotin, 20.0000 Milligram (Mg),Polysorbate 20, Nf, Jpe 0.4000 Milligram (Mg),Histidine Hydrochloride Monohydrate 4.6200 Milligram (Mg),Trehalose Dihydrate, Nf 110.0000 Milligram (Mg),Histidine 2.8000 Milligram (Mg)</t>
+          <t>Mirvetuximab Soravtansine 5.0000 Mg/Ml,Acetic Acid, Glacial 0.2200 Mg/Ml,Polysorbate 20 0.1000 Mg/Ml,Sodium Acetate, Anhydrous 0.5300 Mg/Ml,Sucrose 90.0000 Mg/Ml,Water For Injection 1.0000 Ml</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Padcev, In Combination With Pembrolizumab, Is Indicated For The Treatment Of Adult Patients With Locally Advanced Or Metastatic Urothelial Cancer (Muc).</t>
+          <t>Elahere As Monotherapy Is Indicated For The Treatment Of Adult Patients With Folate Receptor-Alpha (Fr?) Positive, Platinum-Resistant Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer, Who Have Received One To Three Prior Systemic Treatment Regimens.</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Astellas Pharma India Pvt. Ltd.</t>
+          <t>AbbVie Healthcare India Private Limited</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -4211,12 +4335,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Mirvetuximab Soravtansine Injection 5mg/Ml</t>
+          <t>Tegoprazan</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4231,22 +4355,22 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Mirvetuximab Soravtansine 5.0000 Mg/Ml,Acetic Acid, Glacial 0.2200 Mg/Ml,Polysorbate 20 0.1000 Mg/Ml,Sodium Acetate, Anhydrous 0.5300 Mg/Ml,Sucrose 90.0000 Mg/Ml,Water For Injection 1.0000 Ml</t>
+          <t>Ferric Oxide Red Usp Nf 0.0000 Q.S.,Titanium Dioxide 0.0000 Q.S.,Excipients 0.0000 Q.S.,Ferric Oxide Black Usp Nf 0.0000 Q.S.,Tegoprazan 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Film coated tablet</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Elahere As Monotherapy Is Indicated For The Treatment Of Adult Patients With Folate Receptor-Alpha (Fr?) Positive, Platinum-Resistant Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer, Who Have Received One To Three Prior Systemic Treatment Regimens.</t>
+          <t>Tegoprazan Tablets 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease.,Tegoprazan Tablets 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non-Erosive Gastroesophageal Reflux Disease, Gastric Ulcer</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>AbbVie Healthcare India Private Limited</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -4286,7 +4410,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>Semaglutide Injection</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4296,37 +4420,37 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Semaglutide 0.2500 Milligram (Mg)</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Solution for injection</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of - ?	30 Kg/M2 Or Greater (Obesity) Or ?	27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>M/s. VXL Life Sciences</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Alkem Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -4341,7 +4465,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:15</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr"/>
@@ -4356,7 +4480,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Insulin Injection, Soluble (Neutral) Ip 100iu/Ml</t>
+          <t>Human Insulin (Rdna Origin)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4366,22 +4490,22 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Glycerol 16.0000 Mg/Ml,Water For Injection 1.0000 Q.S.,Hydrochloric Acid 1.0000 Q.S. To Adjust Ph,Metacresol 2.5000 Mg/Ml,Sodium Hydroxide 1.0000 Q.S. To Adjust Ph,Human Insulin (Rdna Origin) 100.0000 Iu/Ml</t>
+          <t>Each ml contains: Insulin Human I.P. 100 IU (Human Insulin of rDNA Origin)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Dosage is individual and determined in accordance with the needs of the patient. The individual insulin requirement is usually between 0.3 and 1.0 IU/kg/day.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Diabetes Type I And Type Ii</t>
+          <t>Treatment of diabetes mellitus.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4394,11 +4518,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -4411,22 +4531,34 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:55:21</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sanofi.com/assets/countries/india/docs/science-and-innovation/for-healthcare-profsionals/product-information/pharmaceuticals/insutage-pi.pdf</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/health/documents/community-register/2009/2009100164888/anx_64888_en.pdf</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/health/documents/community-register/2009/2009100164888/anx_64888_en.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Human Insulin (Rdna Origin)</t>
+          <t>Avibactam (As Sodium Salt) 0.5 Gm+Aztreonam 1.5 Gm</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4436,37 +4568,37 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Avibactam (As Sodium Salt)0.5 Gm 0.5000 Gram (G)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Solution for infusion</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Complicated Intra-Abdominal Infection (Ciai),Hospital-Acquired Pneumonia (Hap), Including Ventilator-Associated Pneumonia (Vap),Complicated Urinary Tract Infection (Cuti), Including Pyelonephritis.,Treatment Of Infections Due To Aerobic Gram-Negative Organism?S In Adult Patients With Limited Treatment Options.</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Regenix Drugs Ltd.</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>GUFIC BIOSCIENCES LIMITED</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -4481,7 +4613,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:19</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr"/>
@@ -4491,12 +4623,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Avibactam (As Sodium Salt) 0.5 Gm+Aztreonam 1.5 Gm</t>
+          <t>Insulin Injection, Soluble (Neutral) Ip 100iu/Ml</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4511,22 +4643,22 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Avibactam (As Sodium Salt)0.5 Gm 0.5000 Gram (G)</t>
+          <t>Glycerol 16.0000 Mg/Ml,Water For Injection 1.0000 Q.S.,Hydrochloric Acid 1.0000 Q.S. To Adjust Ph,Metacresol 2.5000 Mg/Ml,Sodium Hydroxide 1.0000 Q.S. To Adjust Ph,Human Insulin (Rdna Origin) 100.0000 Iu/Ml</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Solution for infusion</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Complicated Intra-Abdominal Infection (Ciai),Hospital-Acquired Pneumonia (Hap), Including Ventilator-Associated Pneumonia (Vap),Complicated Urinary Tract Infection (Cuti), Including Pyelonephritis.,Treatment Of Infections Due To Aerobic Gram-Negative Organism?S In Adult Patients With Limited Treatment Options.</t>
+          <t>Diabetes Type I And Type Ii</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>GUFIC BIOSCIENCES LIMITED</t>
+          <t>Regenix Drugs Ltd.</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -4566,7 +4698,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Insulin Glargine Injection</t>
+          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4581,22 +4713,22 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Insulin Glargine 100.0000 Iu/Ml,Sodium Hydroxide 0.0000 Q.S,M-Cresol 2.7000 Milligram (Mg),Glycerol (85%) 20.0000 Milligram (Mg),Zinc* (As Zinc Chloride) 30.0000 Micrograms (?g),Hydrochloric Acid 0.0000 Q.S,Water For Injection 0.0000 Q.S To 1 Ml</t>
+          <t>Diphtheria Toxoid 20.0000 Iu (30 Lf),Tetanus Toxoid 40.0000 Iu (10 Lf),Bordetella Pertussis Antigens- Pertussis Toxoid 25.0000 Micrograms (?g),Bordetella Pertussis Antigens- Filamentous Haemagglutinin 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 D Antigen Units,Aluminium Hydroxide, Hydrated 0.3000 Mg Al,Phenoxyethanol - Ethanol (50 % V/V Solution) Phenoxyethanol 2.5000 ?l,Phenoxyethanol - Ethanol (50 % V/V Solution) Ethanol Anhydrous 2.5000 ?l,Formaldehyde Solution 10.0000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0500 Ml,Water For Injections 0.0000 Upto 0.5 Ml</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Suspension for injection in a prefilled syringe</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Or Above With Diabetes Mellitus, Where Treatment With Insulin Is Required</t>
+          <t>This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Biocon Biologics Limited</t>
+          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -4636,7 +4768,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
+          <t>Insulin Glargine Injection</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4651,22 +4783,22 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Diphtheria Toxoid 20.0000 Iu (30 Lf),Tetanus Toxoid 40.0000 Iu (10 Lf),Bordetella Pertussis Antigens- Pertussis Toxoid 25.0000 Micrograms (?g),Bordetella Pertussis Antigens- Filamentous Haemagglutinin 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 D Antigen Units,Aluminium Hydroxide, Hydrated 0.3000 Mg Al,Phenoxyethanol - Ethanol (50 % V/V Solution) Phenoxyethanol 2.5000 ?l,Phenoxyethanol - Ethanol (50 % V/V Solution) Ethanol Anhydrous 2.5000 ?l,Formaldehyde Solution 10.0000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0500 Ml,Water For Injections 0.0000 Upto 0.5 Ml</t>
+          <t>Insulin Glargine 100.0000 Iu/Ml,Sodium Hydroxide 0.0000 Q.S,M-Cresol 2.7000 Milligram (Mg),Glycerol (85%) 20.0000 Milligram (Mg),Zinc* (As Zinc Chloride) 30.0000 Micrograms (?g),Hydrochloric Acid 0.0000 Q.S,Water For Injection 0.0000 Q.S To 1 Ml</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Suspension for injection in a prefilled syringe</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations</t>
+          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Or Above With Diabetes Mellitus, Where Treatment With Insulin Is Required</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+          <t>Biocon Biologics Limited</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -4706,7 +4838,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Ertapenem Sodium</t>
+          <t>Micronized Purified Flavonoid Fraction 500 Mg Tablets</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4716,37 +4848,38 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Micronized Purified Flavonoid Fraction 500.0000 Milligram (Mg)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>1. Treatment Of Symptoms Related To Venolymphatic Insufficiency (Heavy Legs Pain, Restless Legs Syndrome).
+2.Treatment Of Functional Symptoms Related To Hemorrhoidal Attack.</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>DIVINNE SBR INTERNATIONAL PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SERVIER INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4761,7 +4894,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:26</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr"/>
@@ -4789,19 +4922,19 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Edoxaban Tosylate Monohydrate</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>60 mg, 1 times / day Route: oral</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>to reduce the risk of stroke and systemic embolism (SE) in patients with nonvalvular atrial fibrillation (NVAF).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4809,16 +4942,12 @@
           <t>M/s. MSN Life Sciences Private Limited</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -4831,12 +4960,24 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:23</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:52:06</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>https://ndclist.com/active-ingredients/edoxaban-tosylate-monohydrate</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>https://drugs.ncats.io/drug/972203R4EW</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>https://drugs.ncats.io/drug/972203R4EW</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -4846,7 +4987,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Micronized Purified Flavonoid Fraction 500 Mg Tablets</t>
+          <t>Ertapenem Sodium</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4856,28 +4997,27 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Micronized Purified Flavonoid Fraction 500.0000 Milligram (Mg)</t>
+          <t>Poudre pour solution 1 g d’ertapénem/flacon (sous forme d’ertapénem monosodique). Ingrédients non médicinaux: Hydrogénocarbonate de sodium et hydroxyde de sodium.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Adult patients with severe renal impairment (creatinine clearance ≤30 mL/min/1.73 m2) and end-stage renal disease (creatinine clearance ≤10 mL/min/1.73 m2) should receive 500 mg daily. A supplementary dose of 150 mg is recommended if ertapenem is administered within 6 hours prior to hemodialysis.</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>1. Treatment Of Symptoms Related To Venolymphatic Insufficiency (Heavy Legs Pain, Restless Legs Syndrome).
-2.Treatment Of Functional Symptoms Related To Hemorrhoidal Attack.</t>
+          <t>Complicated Intra-Abdominal Infections; Complicated Skin and Skin Structure Infections, Including Diabetic Foot Infections without Osteomyelitis; Community Acquired Pneumonia; Complicated Urinary Tract Infections Including Pyelonephritis; Acute Pelvic Infections Including Postpartum Endomyometritis, Septic Abortion and Post-Surgical Gynecologic Infections; Prophylaxis of Surgical Site Infection Following Elective Colorectal Surgery.</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>SERVIER INDIA PRIVATE LIMITED</t>
+          <t>DIVINNE SBR INTERNATIONAL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -4885,11 +5025,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -4902,22 +5038,34 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="4" t="inlineStr"/>
-      <c r="P63" s="4" t="inlineStr"/>
+          <t>2026-07-02 00:52:27</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>https://pdf.hres.ca/dpd_pm/00070374.PDF</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/drugInfo.cfm?setid=f74cca2f-e775-4580-acae-3a0c47dd24d9</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/drugInfo.cfm?setid=f74cca2f-e775-4580-acae-3a0c47dd24d9</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Guselkumab</t>
+          <t>Belumosudil Mesylate-Bulk Drug</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4927,37 +5075,37 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>L-Histidine Monohydrochloride Monohydrate 26.6000 Milligram (Mg),L-Methionine 8.0000 Milligram (Mg),Polysorbate 80 10.0000 Milligram (Mg),L-Histidine 11.3000 Milligram (Mg),Edta-Disodium Dihydrate 0.4000 Milligram (Mg),Guselkumab 200.0000 Milligram (Mg),Water For Injection 20.0000 Ml,Sucrose 1700.0000 Milligram (Mg)</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Solution for injection, Solution for infusion</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Ulcerative Colitis,Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Crohn?S Disease</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>MSN Organics Private Limited</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition, dosage, indication</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4972,7 +5120,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
+          <t>2026-07-02 00:56:00</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr"/>
@@ -4982,12 +5130,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Belumosudil Tablets 200 Mg</t>
+          <t>Infliximab</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -5002,22 +5150,22 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Belumosudil Mesylate 200.0000 Milligram (Mg)</t>
+          <t>Infliximab 100.0000 Milligram (Mg),Sodium Phosphate, Monobasic, Monohydrate 2.2000 Milligram (Mg),Sucrose 500.0000 Milligram (Mg),Sodium Phosphate, Dibasic Dihydrate 6.1000 Milligram (Mg),Polysorbate 80 0.5000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Indicated For The Treatment Of Patients 12 Years And Older With Chronic Graftversus-Host Disease(Cgvhd) After Failure Of At Least Two Prior Lines Of Systemic Therapy.</t>
+          <t>Rheumatoid Arthritis,Adult Crohn?S Disease,Paediatric Crohn?S Disease,Ulcerative Colitis,Ankylosing Spondylitis,Psoriatic Arthritis,Psoriasis</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>MSN Laboratories Private Limited</t>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -5057,7 +5205,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Infliximab</t>
+          <t>Velaglucerase Alfa</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5072,22 +5220,22 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Infliximab 100.0000 Milligram (Mg),Sodium Phosphate, Monobasic, Monohydrate 2.2000 Milligram (Mg),Sucrose 500.0000 Milligram (Mg),Sodium Phosphate, Dibasic Dihydrate 6.1000 Milligram (Mg),Polysorbate 80 0.5000 Milligram (Mg)</t>
+          <t>Velaglucerase Alfa 10.0000 Milligram (Mg),Sucrose 200.0000 Milligram (Mg),Sodium Citrate, Dehydrate 51.7600 Milligram (Mg),Citric Acid, Monohydrate 5.0400 Milligram (Mg),Polysorbate 20 0.4400 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>Powder for Solution for Infusion in SDV</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Rheumatoid Arthritis,Adult Crohn?S Disease,Paediatric Crohn?S Disease,Ulcerative Colitis,Ankylosing Spondylitis,Psoriatic Arthritis,Psoriasis</t>
+          <t>Velaglucerase Alfa Is Indicated For Long-Term Enzyme Replacement Therapy (Ert) In Patients With Type 1, And Chronic Neuronopathic (Type 3) Gaucher Disease Who Exhibit Clinically Significant Non-Neurological Manifestations Of The Disease</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
+          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -5127,7 +5275,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Bevacizumab</t>
+          <t>Guselkumab</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5142,22 +5290,22 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bevacizumab 100.0000 Mg/4ml (25 Mg/Ml)</t>
+          <t>L-Histidine Monohydrochloride Monohydrate 26.6000 Milligram (Mg),L-Methionine 8.0000 Milligram (Mg),Polysorbate 80 10.0000 Milligram (Mg),L-Histidine 11.3000 Milligram (Mg),Edta-Disodium Dihydrate 0.4000 Milligram (Mg),Guselkumab 200.0000 Milligram (Mg),Water For Injection 20.0000 Ml,Sucrose 1700.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Concentrate solution for infusion</t>
+          <t>Solution for injection, Solution for infusion</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Hepatocellular Carcinoma (Hcc)</t>
+          <t>Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Ulcerative Colitis,Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Crohn?S Disease</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Limited</t>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -5197,7 +5345,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Velaglucerase Alfa</t>
+          <t>Inactivated Poliomyelitis Vaccine I.P.</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5212,22 +5360,22 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Velaglucerase Alfa 10.0000 Milligram (Mg),Sucrose 200.0000 Milligram (Mg),Sodium Citrate, Dehydrate 51.7600 Milligram (Mg),Citric Acid, Monohydrate 5.0400 Milligram (Mg),Polysorbate 20 0.4400 Milligram (Mg)</t>
+          <t>Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 1 (Mahoney) 29.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 2 (Mef) 7.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 3 (Saukett) 26.0000 D Antigen Units,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Phenoxyethanol 2.5000 ?l,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Ethanol 2.5000 ?l,Formaldehyde Solution 12.5000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0000 Q.S. To 0.5 Ml</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Powder for Solution for Infusion in SDV</t>
+          <t>Suspension for injection</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Velaglucerase Alfa Is Indicated For Long-Term Enzyme Replacement Therapy (Ert) In Patients With Type 1, And Chronic Neuronopathic (Type 3) Gaucher Disease Who Exhibit Clinically Significant Non-Neurological Manifestations Of The Disease</t>
+          <t>Active Immunization Of Infants, Children And Adults For Prevention Of Poliomyelitis</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
+          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -5267,7 +5415,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Avibactam 500 Mg+Aztreonam 1500 Mg</t>
+          <t>Dapagliflozin+Metoprolol Sr</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5282,22 +5430,22 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Aztreonam 1500.0000 Milligram (Mg),Avibactam Sodium Equivalent To Avibactam 500.0000 Milligram (Mg)</t>
+          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Metoprolol Succinate 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>For The Treatment Of The Following Infections In Adult Patients- Complicated Intra Abdominal Infection, Hospital Acquired Pneumonia, Including Ventilator Associated Pneumonia, Complicated Urinary Tract Infection, Including Pyelonephritis. It Is Also Indicated For The Treatment Of Infections Due To Aerobic Gram Negative Organisms In Adult Patients With Limited Treatment Options. Consideration Should Be Given To Official Guidance On The Appropriate Use Of Antibacterial Agents.</t>
+          <t>Heart Failure Post-Acute Myocardial Infarction</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>BDR Pharmaceuticals International Pvt Ltd</t>
+          <t>Eris Lifesciences Limited</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -5402,12 +5550,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Inactivated Poliomyelitis Vaccine I.P.</t>
+          <t>Avibactam 500 Mg+Aztreonam 1500 Mg</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -5422,22 +5570,22 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 1 (Mahoney) 29.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 2 (Mef) 7.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 3 (Saukett) 26.0000 D Antigen Units,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Phenoxyethanol 2.5000 ?l,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Ethanol 2.5000 ?l,Formaldehyde Solution 12.5000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0000 Q.S. To 0.5 Ml</t>
+          <t>Aztreonam 1500.0000 Milligram (Mg),Avibactam Sodium Equivalent To Avibactam 500.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Suspension for injection</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Active Immunization Of Infants, Children And Adults For Prevention Of Poliomyelitis</t>
+          <t>For The Treatment Of The Following Infections In Adult Patients- Complicated Intra Abdominal Infection, Hospital Acquired Pneumonia, Including Ventilator Associated Pneumonia, Complicated Urinary Tract Infection, Including Pyelonephritis. It Is Also Indicated For The Treatment Of Infections Due To Aerobic Gram Negative Organisms In Adult Patients With Limited Treatment Options. Consideration Should Be Given To Official Guidance On The Appropriate Use Of Antibacterial Agents.</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+          <t>BDR Pharmaceuticals International Pvt Ltd</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -5472,12 +5620,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Dapagliflozin+Metoprolol Sr</t>
+          <t>Abiraterone Acetate Tablets Ip</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5492,7 +5640,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Metoprolol Succinate 25.0000 Milligram (Mg)</t>
+          <t>Abiraterone Acetate 1000.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -5502,12 +5650,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Heart Failure Post-Acute Myocardial Infarction</t>
+          <t>For The Treatment Of 1) In Combination With Prednisone For The Treatment Of Patients With Metastatic Castration-Resistant Prostate Cancer Who Have Received Prior Chemotherapy Containing Docetaxel. 2) Indicated For The Treatment Of Metastatic Castration Resistant Prostate Cancer In Adult Men Who Are Asymptomatic Or Mildly Symptomatic After Failure Of Androgen Deprivation Therapy In Whom Chemotherapy Is Not Yet Clinically Indicated, With Prednisone Or Prednisolone.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Limited</t>
+          <t>MSN Laboratories Private Limited</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -5547,7 +5695,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Abiraterone Acetate Tablets Ip</t>
+          <t>Belumosudil Tablets 200 Mg</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -5562,7 +5710,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Abiraterone Acetate 1000.0000 Milligram (Mg)</t>
+          <t>Belumosudil Mesylate 200.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -5572,7 +5720,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>For The Treatment Of 1) In Combination With Prednisone For The Treatment Of Patients With Metastatic Castration-Resistant Prostate Cancer Who Have Received Prior Chemotherapy Containing Docetaxel. 2) Indicated For The Treatment Of Metastatic Castration Resistant Prostate Cancer In Adult Men Who Are Asymptomatic Or Mildly Symptomatic After Failure Of Androgen Deprivation Therapy In Whom Chemotherapy Is Not Yet Clinically Indicated, With Prednisone Or Prednisolone.</t>
+          <t>Indicated For The Treatment Of Patients 12 Years And Older With Chronic Graftversus-Host Disease(Cgvhd) After Failure Of At Least Two Prior Lines Of Systemic Therapy.</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5612,12 +5760,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Belumosudil Mesylate-Bulk Drug</t>
+          <t>Bevacizumab</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5627,37 +5775,37 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Bevacizumab 100.0000 Mg/4ml (25 Mg/Ml)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Concentrate solution for infusion</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Hepatocellular Carcinoma (Hcc)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>MSN Organics Private Limited</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Dr Reddys Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5672,7 +5820,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:30</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
@@ -5687,7 +5835,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Hepatitis A (Live) Vaccine, Freeze-Dried Injection</t>
+          <t>Tetanus Vaccine (Adsorbed) I.P.-Ready To Fill Bulk (Rtfb)</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -5697,37 +5845,37 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Live Attenuated Hepatitis A Virus 6.5000 Log Ccid50</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Vaccines (Lyophilized)</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>For Active Immunization Against Infection Caused By Hepatitis A Virus</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Joint Force Pharamchem Pvt. Ltd.,</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>INDIAN IMMUNOLOGICAL LIMITED</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition, dosage, indication</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -5742,12 +5890,24 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N75" s="4" t="inlineStr"/>
-      <c r="O75" s="4" t="inlineStr"/>
-      <c r="P75" s="4" t="inlineStr"/>
+          <t>2026-07-02 00:55:29</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P75" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5757,7 +5917,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Tetanus Vaccine (Adsorbed) I.P.-Ready To Fill Bulk (Rtfb)</t>
+          <t>Hepatitis A (Live) Vaccine, Freeze-Dried Injection</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5767,37 +5927,37 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Live Attenuated Hepatitis A Virus 6.5000 Log Ccid50</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Vaccines (Lyophilized)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>For Active Immunization Against Infection Caused By Hepatitis A Virus</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>INDIAN IMMUNOLOGICAL LIMITED</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Joint Force Pharamchem Pvt. Ltd.,</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>composition, dosage, indication</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -5812,7 +5972,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:23</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
@@ -6032,12 +6192,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Tegoprazan Tablets 50 Mg And 25 Mg</t>
+          <t>Fluticasone Furoate+Umeclidinium+Vilanterol</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6052,22 +6212,22 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Tegoprazan 25.0000 Milligram (Mg)</t>
+          <t>Vilanterol 12.5000 Micrograms (?g),Umeclidinium 31.2500 Micrograms (?g),Fluticasone Furoate 100.0000 Micrograms (?g)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Inhalation Preparations</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Tegoprazan Tablet 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non Erosive Gastroesophageal Reflux Disease And Gastric Ulcer,Tegoprazan Tablet 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease</t>
+          <t>Indicated For The Maintenance Treatment Of Asthma In Patients Aged 18 Years And Older.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Dr. Reddys Laboratories Limited</t>
+          <t>Zydus Healthcare Limited</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -6102,12 +6262,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Semaglutide Injection</t>
+          <t>Bilastine 3.3 Mg+Dextromethorphan Hydrobromide 10 Mg+Phenylephrine Hydrochloride 5 Mg Syrup</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -6122,22 +6282,22 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Semaglutide 1.0000 Mg/1.5 Ml</t>
+          <t>Dextromethorphan Hydrobromide 10.0000 Milligram (Mg),Bilastine 3.3000 Milligram (Mg),Phenylephrine Hydrochloride 5.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Syrup</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of 30 Kg/M2 Or Greater (Obesity). Or 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia).</t>
+          <t>For Relief Of Coughs And Upper Respiratory Symptoms, Including Nasal Congestion, Associated With Allergy Or The Common Cold</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Natco Pharma Limited</t>
+          <t>Windlas Biotech Limited</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -6177,7 +6337,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Fluticasone Furoate+Umeclidinium+Vilanterol</t>
+          <t>Umeclidinium+Vilanterol</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6192,17 +6352,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Vilanterol 12.5000 Micrograms (?g),Umeclidinium 31.2500 Micrograms (?g),Fluticasone Furoate 100.0000 Micrograms (?g)</t>
+          <t>Vilanterol 25.0000 Micrograms (?g),Umeclidinium 62.5000 Micrograms (?g)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Inhalation Preparations</t>
+          <t>Inhalation Powder</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Indicated For The Maintenance Treatment Of Asthma In Patients Aged 18 Years And Older.</t>
+          <t>For The Maintenance Treatment Of Patients With Chronic Obstructive Pulmonary Disease (Copd).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6247,7 +6407,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Umeclidinium+Vilanterol</t>
+          <t>Eplerenone+Torsemide</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -6262,22 +6422,22 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Vilanterol 25.0000 Micrograms (?g),Umeclidinium 62.5000 Micrograms (?g)</t>
+          <t>Torsemide 10.0000 Milligram (Mg),Eplerenone 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Inhalation Powder</t>
+          <t>Uncoated Tablets</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>For The Maintenance Treatment Of Patients With Chronic Obstructive Pulmonary Disease (Copd).</t>
+          <t>Indicated In Patients With Congestive Heart Failure.</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Zydus Healthcare Limited</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -6312,12 +6472,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Bilastine 3.3 Mg+Dextromethorphan Hydrobromide 10 Mg+Phenylephrine Hydrochloride 5 Mg Syrup</t>
+          <t>Tegoprazan Tablets 50 Mg And 25 Mg</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6332,22 +6492,22 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Dextromethorphan Hydrobromide 10.0000 Milligram (Mg),Bilastine 3.3000 Milligram (Mg),Phenylephrine Hydrochloride 5.0000 Milligram (Mg)</t>
+          <t>Tegoprazan 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Syrup</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>For Relief Of Coughs And Upper Respiratory Symptoms, Including Nasal Congestion, Associated With Allergy Or The Common Cold</t>
+          <t>Tegoprazan Tablet 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non Erosive Gastroesophageal Reflux Disease And Gastric Ulcer,Tegoprazan Tablet 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Limited</t>
+          <t>Dr. Reddys Laboratories Limited</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -6382,12 +6542,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Eplerenone+Torsemide</t>
+          <t>Semaglutide Injection</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -6402,22 +6562,22 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Torsemide 10.0000 Milligram (Mg),Eplerenone 25.0000 Milligram (Mg)</t>
+          <t>Semaglutide 1.0000 Mg/1.5 Ml</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Uncoated Tablets</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Indicated In Patients With Congestive Heart Failure.</t>
+          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of 30 Kg/M2 Or Greater (Obesity). Or 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia).</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
+          <t>Natco Pharma Limited</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -6512,7 +6672,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:27</t>
+          <t>2026-07-02 00:56:40</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
@@ -6722,7 +6882,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:33</t>
+          <t>2026-07-02 00:56:03</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr"/>
@@ -6750,19 +6910,19 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Solution for injection, 100 mg/mL (as sugammadex sodium) hydrochloric acid (for pH adjustment), sodium hydroxide (for pH adjustment), water for injection</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Injection (single dose vials) 200mg/2mL (100mg/mL), 500mg/5mL (100mg/mL). Administer as single IV bolus injection infused over 10 seconds into existing IV line. For rocuronium and vecuronium, adult dosage is 4 mg/kg (if spontaneous recovery of the twitch response has reached 1-2 post-tetanic counts (PTC)) or 2 mg/kg (if spontaneous recovery has reached the reappearance of the second twitch (T2)). For rocuronium only, adult dosage is 16 mg/kg if there is a clinical need to reverse neuromuscular blockade soon (~3 minutes) after administration of a single dose of 1.2 mg/kg.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Reversal of neuromuscular blockade induced by rocuronium</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -6770,16 +6930,12 @@
           <t>BDR Pharmaceuticals International Pvt Ltd</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
           <t>CDSCO</t>
@@ -6792,12 +6948,24 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:01:29</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="inlineStr"/>
+          <t>2026-07-02 00:55:47</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>https://pdf.hres.ca/dpd_pm/00076541.PDF</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rxlist.com/sugammadex_sodium/generic-drug.htm</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/health/documents/community-register/2023/20230526159142/anx_159142_en.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -6825,49 +6993,61 @@
           <t>Not Available</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>For acute myeloid leukemia: Adults—At first, 100 milligrams (mg) once a day. Your doctor will gradually increase your dose each week. However, the dose is usually not more than 400 mg per day when given with azacitidine or decitabine or not more than 600 mg per day when given with low-dose cytarabine. For chronic lymphocytic leukemia or small lymphocytic lymphoma: Adults—At first, 20 milligrams (mg) once a day. Your doctor will gradually increase your dose each week for 5 weeks (ramp-up). However, the dose is usually not more than 400 mg per day.</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Indicated for patients with chronic lymphocytic leukemia (CLL) or small lymphocytic lymphoma (SLL). Indicated in combination with azacitidine or decitabine or low-dose cytarabine for treatment in adults (≥75 years) who are newly-diagnosed acute myeloid leukemia (AML) or who have comorbidities that preclude use of intensive induction chemotherapy.</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Natco Pharma Limited</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>composition</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:52:43</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>Natco Pharma Limited</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>composition, dosage, indication</t>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>CDSCO</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
-        </is>
-      </c>
-      <c r="M91" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01 01:00:35</t>
-        </is>
-      </c>
-      <c r="N91" s="4" t="inlineStr"/>
-      <c r="O91" s="4" t="inlineStr"/>
-      <c r="P91" s="4" t="inlineStr"/>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mayoclinic.org/drugs-supplements/venetoclax-oral-route/description/drg-20311676</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>https://reference.medscape.com/drug/venclexta-venetoclax-1000078</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7002,7 +7182,7 @@
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:44</t>
+          <t>2026-07-02 00:56:06</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr"/>
@@ -7157,12 +7337,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Test Drug</t>
+          <t>Polmacoxib</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>01-JUL-2026</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -7187,7 +7367,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>OpenAI Pharma</t>
+          <t>RESPECT LABS LLP</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
@@ -7207,20 +7387,454 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://www.cdsco.gov.in</t>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00:02</t>
+          <t>2026-07-02 00:56:44</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Lazertinib Film Coated Tablets 80mg And 240 Mg</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>01-JUL-2026</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Lazertinib Mesylate Monohydrate 96.4800 Milligram (Mg),Hydrophobic Colloidal Silica 1.9000 Milligram (Mg),Microcrystalline Cellulose 218.3200 Milligram (Mg),Mannitol 50.0000 Milligram (Mg),Croscarmellose Sodium 9.5000 Milligram (Mg),Magnesium Stearate 3.8000 Milligram (Mg),Opadry Qx 321a220024 Yellow 11.4000 Milligram (Mg),Purified Water 0.0000 Removed During Processing</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>In Combination With Amivantamab Is Indicated For The First-Line Treatment Of Adult Patients With Locally Advanced Or Metastatic Non-Small Cell Lung Cancer (Nsclc) With Epidermal Growth Factor Receptor (Egfr) Exon 19 Deletions Or Exon 21 L858r Substitution Mutations.</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
+        </is>
+      </c>
+      <c r="M97" s="4" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 00:50</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr"/>
+      <c r="O97" s="4" t="inlineStr"/>
+      <c r="P97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Brexpiprazole Tablets 0.25mg/0.5mg/1mg/2mg/3mg/4mg</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-2026</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Brexpiprazole Tablets 0.25mg 0.2500 Milligram (Mg)</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Brexpiprazole Is Indicated For The Treatment Of Schizophrenia In Adult Patients.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 00:50</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Semaglutide Injection (Synthetic Origin)</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>01-JUL-2026</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Semaglutide 0.6800 Mg/Ml</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Solution for injection</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Semaglutide Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adult With An Initial Body Mass Index (Bmi) Of ? 30 Kg/M2 Or Greater (Obesity) Or ? 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia).</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Emcure Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 00:50</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr"/>
+      <c r="O99" s="4" t="inlineStr"/>
+      <c r="P99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Eluxadoline Tablets 75 Mg And 100 Mg</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-2026</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Both BD &amp; FF</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Eluxadoline 90.0000 %</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Tablets</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Indicated In Adults For The Treatment Of Irritable Bowel Syndrome With Diarrhea (Ibs-D)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 00:50</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Semaglutide Injection 2mg/3ml, 4mg/3ml &amp; 8mg/3ml</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>01-JUL-2026</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Semaglutide 0.6800 Mg/Ml</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Pre Filled Pen</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Semaglutide Is Indicated For The Treatment Of Adults With Insufficiently Controlled Type 2 Diabetes Mellitus As An Adjunct To Diet And Exercise
+As Monotherapy, When Metformin-Based Therapy Is Considered Inappropriate Due To Intolerance Or Contraindications.
+In Addition To Other Medicinal Products For The Treatment Of Diabetes.</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Precise Biopharma Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
+        </is>
+      </c>
+      <c r="M101" s="4" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 00:50</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr"/>
+      <c r="O101" s="4" t="inlineStr"/>
+      <c r="P101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Test Drug</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Pharma</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>composition, dosage, indication</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>CDSCO</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cdsco.gov.in</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:55:12</t>
+        </is>
+      </c>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="O102" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P102" s="5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P96"/>
+  <autoFilter ref="A1:P102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/exports/cdsco_approvals.xlsx
+++ b/data/exports/cdsco_approvals.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drug Approvals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ICD Mappings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$R$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Drug Approvals'!$A$1:$R$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ICD Mappings'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,10 +34,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
@@ -89,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,12 +109,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -683,7 +675,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Nelarabine bulk drug &amp; Nelarabine Injection 250mg/50ml(5mg/ml)</t>
+          <t>Enmetazobactam bulk drug &amp; Cefipime 2gm and Enmetazobactam 500mg Dry powder for injection</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -708,7 +700,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t> For the treatment of patients with T-cell Lymphoblastic leukemia and T-cell Lymphoblastic lymphoma in adult and pediatric patients age 1 year and older whose disease has not responded to or has relapsed following treatment with at least two chemotherapy regimens</t>
+          <t>Indicated for the treatment of patients 18 years of age and older for:  Complicated urinary tract infection(CUTI) including acute pyelonephritis  Hospital-acquired pneumonia (HAP), including ventilator- associated pneumonia (VAP)  Bacteremia with complicated urinary tract infection or hospital- acquired pneumonia</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -748,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>46211.74147719907</v>
+        <v>46211.74147793982</v>
       </c>
     </row>
     <row r="4">
@@ -759,7 +751,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Enmetazobactam bulk drug &amp; Cefipime 2gm and Enmetazobactam 500mg Dry powder for injection</t>
+          <t>Nelarabine bulk drug &amp; Nelarabine Injection 250mg/50ml(5mg/ml)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -784,7 +776,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Indicated for the treatment of patients 18 years of age and older for:  Complicated urinary tract infection(CUTI) including acute pyelonephritis  Hospital-acquired pneumonia (HAP), including ventilator- associated pneumonia (VAP)  Bacteremia with complicated urinary tract infection or hospital- acquired pneumonia</t>
+          <t> For the treatment of patients with T-cell Lymphoblastic leukemia and T-cell Lymphoblastic lymphoma in adult and pediatric patients age 1 year and older whose disease has not responded to or has relapsed following treatment with at least two chemotherapy regimens</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -824,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>46211.74147793982</v>
+        <v>46211.74147719907</v>
       </c>
     </row>
     <row r="5">
@@ -911,7 +903,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 5 Ml Vial</t>
+          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 10 Ml Vial</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -926,7 +918,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Insulin Glargine (R Dna Origin) 100.0000 Iu/Ml,M-Cresol 2.7000 Milligram (Mg)</t>
+          <t>Insulin Glargine (R-Dna) 100.0000 Iu,M-Cresol (As Preservative) 2.7000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -936,7 +928,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
+          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With  Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -959,7 +951,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -987,7 +979,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 10 Ml Vial</t>
+          <t>Insulin Glargine Injection (Rdna Origin) 100 Iu/Ml, 5 Ml Vial</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -1002,7 +994,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Insulin Glargine (R-Dna) 100.0000 Iu,M-Cresol (As Preservative) 2.7000 Milligram (Mg)</t>
+          <t>Insulin Glargine (R Dna Origin) 100.0000 Iu/Ml,M-Cresol 2.7000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1012,7 +1004,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With  Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
+          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Of Above With Diabetes Mellitus, Where Treatment With Insulin Is Required.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1035,7 +1027,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -1291,7 +1283,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Whole Cell Pertussis Antigen Bulk (Thiomersal ? Free)</t>
+          <t>Hib Conjugate Bulk (Thiomersal ? Free)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1304,19 +1296,19 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Puriöed Capsular Polysaccharide of Hib (PRP) covalently S linked to 20 to 36.7 µg of Tetanus Toxoid 11 µg .......................................................... +++ AI (as AIPO ) ≤ 1.25 mg 4 S .................................................................................................... Preservative: Thiomersal BP/ Ph.Eur 0.01% w/v S</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>0.5 mL</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Active Immunization against Pertussis</t>
+          <t>Active Immunization against Diphtheria, Tetanus, Pertussis, Hepatitis B and Haemophilus inøuenzae type b diseases.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1324,42 +1316,38 @@
           <t>Biological E - Shameerpet</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>composition, dosage</t>
-        </is>
-      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
       <c r="K11" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:32:36</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>https://...</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>https://...</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr">
+          <t>2026-07-02 00:53:23</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
         </is>
@@ -1427,7 +1415,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -1450,12 +1438,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Tegoprazan</t>
+          <t>Hepatitis B Bulk  (Thiomersal ? Free)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1470,22 +1458,22 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>7-[[(4S)-5,7-difluoro-3,4-dihydro-2H-chromen-4-yl] oxy]-N, N,2-trimethyl-3-H-benzimidazole-5-carboxamide</t>
+          <t>For Hep B Hepatitis B Vaccine (rDNA) BP (Adult) [Brand: BEVAC]: Each Dose of 1 mL contains Purified HBsAg 20 µg, Aluminium Hydroxide gel equivalent to Al 0.5 mg, Preservative: Thiomersal BP 0.05 mg. Recombinant HBs antigen produced in Pichia pastoris (Yeast). For Hep B Hepatitis B Vaccine (rDNA) BP (Paediatric) [Brand: BEVAC]: Each Dose of 0.5 mL contains Purified HBsAg 10 µg, Aluminium Hydroxide gel equivalent to Al 0.25 mg, Preservative: Thiomersal BP 0.025 mg. Recombinant HBs antigen produced in Pichia pastoris (Yeast).</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>50mg tablets, 100mg</t>
+          <t>Adult: Each Dose of 1 mL. Paediatric: Each Dose of 0.5 mL.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>GERD, peptic ulcers, H. pylori eradication</t>
+          <t>Active Immunization against infection caused by Hepatitis B.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>AMI LIFESCIENCES PRIVATE LIMITED</t>
+          <t>Biological E - Shameerpet</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -1499,29 +1487,29 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:53:00</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
-        </is>
-      </c>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
+          <t>2026-07-02 00:54:01</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
         </is>
       </c>
       <c r="Q13" s="6" t="b">
@@ -1539,7 +1527,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hepatitis B Bulk  (Thiomersal ? Free)</t>
+          <t>Whole Cell Pertussis Antigen Bulk (Thiomersal ? Free)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1552,19 +1540,19 @@
           <t>Bulk Drug</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>For Hep B Hepatitis B Vaccine (rDNA) BP (Adult) [Brand: BEVAC]: Each Dose of 1 mL contains Purified HBsAg 20 µg, Aluminium Hydroxide gel equivalent to Al 0.5 mg, Preservative: Thiomersal BP 0.05 mg. Recombinant HBs antigen produced in Pichia pastoris (Yeast). For Hep B Hepatitis B Vaccine (rDNA) BP (Paediatric) [Brand: BEVAC]: Each Dose of 0.5 mL contains Purified HBsAg 10 µg, Aluminium Hydroxide gel equivalent to Al 0.25 mg, Preservative: Thiomersal BP 0.025 mg. Recombinant HBs antigen produced in Pichia pastoris (Yeast).</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Adult: Each Dose of 1 mL. Paediatric: Each Dose of 0.5 mL.</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Active Immunization against infection caused by Hepatitis B.</t>
+          <t>Active Immunization against Pertussis</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1572,38 +1560,42 @@
           <t>Biological E - Shameerpet</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>composition, dosage</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02 00:54:01</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
-        <is>
-          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="inlineStr">
-        <is>
-          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
+          <t>2026-07-08 17:32:36</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>https://...</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>https://...</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
         </is>
@@ -1618,12 +1610,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Hib Conjugate Bulk (Thiomersal ? Free)</t>
+          <t>Tegoprazan</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1638,22 +1630,22 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Puriöed Capsular Polysaccharide of Hib (PRP) covalently S linked to 20 to 36.7 µg of Tetanus Toxoid 11 µg .......................................................... +++ AI (as AIPO ) ≤ 1.25 mg 4 S .................................................................................................... Preservative: Thiomersal BP/ Ph.Eur 0.01% w/v S</t>
+          <t>7-[[(4S)-5,7-difluoro-3,4-dihydro-2H-chromen-4-yl] oxy]-N, N,2-trimethyl-3-H-benzimidazole-5-carboxamide</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>0.5 mL</t>
+          <t>50mg tablets, 100mg</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Active Immunization against Diphtheria, Tetanus, Pertussis, Hepatitis B and Haemophilus inøuenzae type b diseases.</t>
+          <t>GERD, peptic ulcers, H. pylori eradication</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Biological E - Shameerpet</t>
+          <t>AMI LIFESCIENCES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -1667,29 +1659,29 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:53:23</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
-        </is>
-      </c>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>https://www.biologicale.com/pdf/Product_VB_International_Marketing.pdf</t>
+          <t>2026-07-02 00:53:00</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ijpsjournal.com/article/Tegoprazan+A+NextGeneration+PCAB+Redefining+Acid+Suppression</t>
         </is>
       </c>
       <c r="Q15" s="6" t="b">
@@ -1707,7 +1699,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Dulaglutide</t>
+          <t>Denosumab</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1717,12 +1709,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Both BD &amp; FF</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Dulaglutide 0.7500 Milligram (Mg),Trisodium Citrate Dihydrate 1.3700 Milligram (Mg),Citric Acid Anhydrous 0.0700 Milligram (Mg),Mannitol 23.2000 Milligram (Mg),Polysorbate 80 0.1000 Milligram (Mg),Water For Injection 0.5000 Ml</t>
+          <t>Denosumab 60.0000 Mg/Ml,Sorbitol 47.0000 Mg/Ml,Polysorbate 20 0.0100 Mg/Ml,Glacial Acetic Acid 1.0600 Mg/Ml</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1732,7 +1724,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Dulaglutide Is A Glucagon-Like Peptide-1 (Glp-1) Receptor Agonist Indicated: ? As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus. ? To Reduce The Risk Of Major Adverse Cardiovascular Events In Adults With Type 2 Diabetes Mellitus Who Have Established Cardiovascular Disease Or Multiple Cardiovascular Risk Factors</t>
+          <t>Indications For Pfs,Treatment Of Postmenopausal Women With Osteoporosis At High Risk For Fracture,Treatment Of Bone Loss In Men Receiving Androgen Deprivation Therapy For Prostate Cancer,Treatment Of Bone Loss In Women Receiving Adjuvant Aromatase Inhibitor Therapy For Breast Cancer,Indications For Vials,Bone Metastasis From Solid Tumors,Giant Cell Tumor Of Bone</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1755,7 +1747,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -1831,7 +1823,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -1859,7 +1851,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Denosumab</t>
+          <t>Dulaglutide</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1869,12 +1861,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Both BD &amp; FF</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Denosumab 60.0000 Mg/Ml,Sorbitol 47.0000 Mg/Ml,Polysorbate 20 0.0100 Mg/Ml,Glacial Acetic Acid 1.0600 Mg/Ml</t>
+          <t>Dulaglutide 0.7500 Milligram (Mg),Trisodium Citrate Dihydrate 1.3700 Milligram (Mg),Citric Acid Anhydrous 0.0700 Milligram (Mg),Mannitol 23.2000 Milligram (Mg),Polysorbate 80 0.1000 Milligram (Mg),Water For Injection 0.5000 Ml</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1884,7 +1876,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Indications For Pfs,Treatment Of Postmenopausal Women With Osteoporosis At High Risk For Fracture,Treatment Of Bone Loss In Men Receiving Androgen Deprivation Therapy For Prostate Cancer,Treatment Of Bone Loss In Women Receiving Adjuvant Aromatase Inhibitor Therapy For Breast Cancer,Indications For Vials,Bone Metastasis From Solid Tumors,Giant Cell Tumor Of Bone</t>
+          <t>Dulaglutide Is A Glucagon-Like Peptide-1 (Glp-1) Receptor Agonist Indicated: ? As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus. ? To Reduce The Risk Of Major Adverse Cardiovascular Events In Adults With Type 2 Diabetes Mellitus Who Have Established Cardiovascular Disease Or Multiple Cardiovascular Risk Factors</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1907,7 +1899,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2287,7 +2279,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2359,7 +2351,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2369,17 +2361,17 @@
           <t>2026-07-02 00:54:31</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
       </c>
-      <c r="O24" s="9" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
       </c>
-      <c r="P24" s="9" t="inlineStr">
+      <c r="P24" s="3" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
@@ -2443,7 +2435,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2453,17 +2445,17 @@
           <t>2026-07-02 00:54:49</t>
         </is>
       </c>
-      <c r="N25" s="10" t="inlineStr">
+      <c r="N25" s="6" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
       </c>
-      <c r="O25" s="10" t="inlineStr">
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
       </c>
-      <c r="P25" s="10" t="inlineStr">
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
@@ -2527,7 +2519,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2537,17 +2529,17 @@
           <t>2026-07-02 00:54:15</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>http://www.metroapi.com/assets/images/mail-signatures/Metrochem-Products-Brochure.pdf</t>
         </is>
       </c>
-      <c r="O26" s="9" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>https://www.pharmacompass.com/pharma-services/api-manufacturing-services/metrochem-api-private-limited</t>
         </is>
       </c>
-      <c r="P26" s="9" t="inlineStr">
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>http://www.metroapi.com/assets/images/mail-signatures/Metrochem-Products-Brochure.pdf</t>
         </is>
@@ -2615,7 +2607,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2795,7 +2787,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Glimepiride Ip+Metformin Hydrochloride Ip (As Extended Release)+Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin</t>
+          <t>Dapagliflozin+Metformin Hydrochloride Sr+Pioglitazone</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2810,7 +2802,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin 100.0000 Milligram (Mg),Glimepiride 1.0000 Milligram (Mg),Metformin Hydrochloride (As Extended Release) 1000.0000 Milligram (Mg)</t>
+          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Pioglitazone Hydrochloride 15.0000 Milligram (Mg),Metformin Hydrochloride Sr 1000.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -2820,12 +2812,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>For The Treatment Of Patients With Type Ii Diabetes Mellitus</t>
+          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
+          <t>Eris Lifesciences Limited</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -2843,7 +2835,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2866,12 +2858,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Semaglutide Injection</t>
+          <t>Brentuximab Vedotin 50 Milligram (Mg)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2886,22 +2878,22 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Semaglutide 0.6800 Mg/Ml (2mg/3ml)</t>
+          <t>Brentuximab Vedotin 50.0000 Milligram (Mg),Citric Acid Monohydrate 2.1000 Milligram (Mg),Sodium Citrate Dihydrate 56.1000 Milligram (Mg),?,?-Trehalose Dihydrate 700.0000 Milligram (Mg),Polysorbate 80 2.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Indicated For The Treatment Of Adults With Insufficiently Controlled Type 2 Diabetes Mellitus As An Adjunct To Diet And Exercise ? As Monotherapy, When Metformin Is Considered Inappropriate Due To Intolerance Or Contraindications. ? In Addition To Other Medicinal Products For The Treatment Of Diabetes.</t>
+          <t>1. Previously Untreated Stage Iii Or Iv Classical Hodgkin Lymphoma (Chl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Stage Iii Or Iv Chl, In Combination With Doxorubicin, Vinblastine, And Dacarbazine.  Adcetris Is Indicated For Adult Patients With Previously Untreated Cd30+ Stage Iib With Risk Factors, Stage Iii Or Stage Iv Hl In Combination With Etoposide, Cyclophosphamide, Doxorubicin, Dacarbazine, Dexamethasone (Brecadd),2. Classical Hodgkin Lymphoma (Chl) Consolidation Adcetris Is Indicated For The Treatment Of Adult Patients With Chl At High Risk Of Relapse Or Progression As Post-Autologous Hematopoietic Stem Cell Transplantation (Auto-Hsct) Consolidation.,3. Relapsed Classical Hodgkin Lymphoma (Chl) Adcetris Is Indicated For The Treatment Of Adult Patients With Chl After Failure Of Auto-Hsct Or After Failure Of At Least Two Prior Multi-Agent Chemotherapy Regimens In Patients Who Are Not Auto-Hsct Candidates.,4. Previously Untreated Systemic Anaplastic Large Cell Lymphoma (Salcl) Or Other Cd30- Expressing Peripheral T-Cell Lymphomas (Ptcl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Salcl Or Other Cd30-Expressing Ptcl, Including Angioimmunoblastic T-Cell Lymphoma And Ptcl Not Otherwise Specified, In Combination With Cyclophosphamide, Doxorubicin, And Prednisone.,5. Relapsed Systemic Anaplastic Large Cell Lymphoma (Salcl) Adcetris Is Indicated For The Treatment Of Adult Patients With Salcl After Failure Of At Least One Prior Multi-Agent Chemotherapy Regimen.,6. Relapsed Primary Cutaneous Anaplastic Large Cell Lymphoma (Pcalcl) Or Cd30- Expressing Mycosis Fungoides (Mf) Adcetris Is Indicated For The Treatment Of Adult Patients With Pcalcl Or Cd30-Expressing Mf Who Have Received Prior Systemic Therapy.</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Dr. Reddys Laboratories Limited</t>
+          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -2919,7 +2911,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L31" s="10" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -2942,12 +2934,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin+Metformin Hydrochloride Sr+Pioglitazone</t>
+          <t>Semaglutide Injection</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2962,22 +2954,22 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Pioglitazone Hydrochloride 15.0000 Milligram (Mg),Metformin Hydrochloride Sr 1000.0000 Milligram (Mg)</t>
+          <t>Semaglutide 0.6800 Mg/Ml (2mg/3ml)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Injection</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
+          <t>Indicated For The Treatment Of Adults With Insufficiently Controlled Type 2 Diabetes Mellitus As An Adjunct To Diet And Exercise ? As Monotherapy, When Metformin Is Considered Inappropriate Due To Intolerance Or Contraindications. ? In Addition To Other Medicinal Products For The Treatment Of Diabetes.</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Limited</t>
+          <t>Dr. Reddys Laboratories Limited</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -2995,7 +2987,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -3071,7 +3063,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -3094,12 +3086,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Brentuximab Vedotin 50 Milligram (Mg)</t>
+          <t>Glimepiride Ip+Metformin Hydrochloride Ip (As Extended Release)+Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3114,22 +3106,22 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Brentuximab Vedotin 50.0000 Milligram (Mg),Citric Acid Monohydrate 2.1000 Milligram (Mg),Sodium Citrate Dihydrate 56.1000 Milligram (Mg),?,?-Trehalose Dihydrate 700.0000 Milligram (Mg),Polysorbate 80 2.0000 Milligram (Mg)</t>
+          <t>Sitagliptin Phosphate Monohydrate Ip Equivalent To Sitagliptin 100.0000 Milligram (Mg),Glimepiride 1.0000 Milligram (Mg),Metformin Hydrochloride (As Extended Release) 1000.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1. Previously Untreated Stage Iii Or Iv Classical Hodgkin Lymphoma (Chl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Stage Iii Or Iv Chl, In Combination With Doxorubicin, Vinblastine, And Dacarbazine.  Adcetris Is Indicated For Adult Patients With Previously Untreated Cd30+ Stage Iib With Risk Factors, Stage Iii Or Stage Iv Hl In Combination With Etoposide, Cyclophosphamide, Doxorubicin, Dacarbazine, Dexamethasone (Brecadd),2. Classical Hodgkin Lymphoma (Chl) Consolidation Adcetris Is Indicated For The Treatment Of Adult Patients With Chl At High Risk Of Relapse Or Progression As Post-Autologous Hematopoietic Stem Cell Transplantation (Auto-Hsct) Consolidation.,3. Relapsed Classical Hodgkin Lymphoma (Chl) Adcetris Is Indicated For The Treatment Of Adult Patients With Chl After Failure Of Auto-Hsct Or After Failure Of At Least Two Prior Multi-Agent Chemotherapy Regimens In Patients Who Are Not Auto-Hsct Candidates.,4. Previously Untreated Systemic Anaplastic Large Cell Lymphoma (Salcl) Or Other Cd30- Expressing Peripheral T-Cell Lymphomas (Ptcl), In Combination With Chemotherapy Adcetris Is Indicated For The Treatment Of Adult Patients With Previously Untreated Salcl Or Other Cd30-Expressing Ptcl, Including Angioimmunoblastic T-Cell Lymphoma And Ptcl Not Otherwise Specified, In Combination With Cyclophosphamide, Doxorubicin, And Prednisone.,5. Relapsed Systemic Anaplastic Large Cell Lymphoma (Salcl) Adcetris Is Indicated For The Treatment Of Adult Patients With Salcl After Failure Of At Least One Prior Multi-Agent Chemotherapy Regimen.,6. Relapsed Primary Cutaneous Anaplastic Large Cell Lymphoma (Pcalcl) Or Cd30- Expressing Mycosis Fungoides (Mf) Adcetris Is Indicated For The Treatment Of Adult Patients With Pcalcl Or Cd30-Expressing Mf Who Have Received Prior Systemic Therapy.</t>
+          <t>For The Treatment Of Patients With Type Ii Diabetes Mellitus</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -3147,7 +3139,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -3527,7 +3519,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -3603,7 +3595,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -3679,7 +3671,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -3783,7 +3775,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Levocarnitine I.P, U.S.P, E.P</t>
+          <t>Elobixibat Tablets 10 Mg</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -3793,27 +3785,27 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Magnesium stearate, microcrystalline cellulose and povidone</t>
+          <t>Ferric Oxide Yellow Usp-Nf 0.0000 Not Applicable (Na),Excipients 0.0000 Q.S.,Titanium Dioxide 0.0000 Not Applicable (Na),Elobixibat Hydrate Eq. To Elobixibat 10.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Adults: The recommended oral dosage for adults is 990 mg two or three times a day using the 330 mg tablets, depending on clinical response. Infants and children: The recommended oral dosage for infants and children is between 50 and 100 mg/kg/day in divided doses, with a maximum of 3 g/day. Dosage should begin at 50 mg/kg/day. The exact dosage will depend on clinical response.</t>
+          <t>film coated tablet</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Levocarnitine is indicated in the treatment of primary systemic carnitine deficiency. In the reported cases, the clinical presentation consisted of recurrent episodes of Reye-like encephalopathy, hypoketotic hypoglycemia, and/or cardiomyopathy. Associated symptoms included hypotonia, muscle weakness and failure to thrive. A diagnosis of primary carnitine deficiency requires that serum, red cell and/or tissue carnitine levels be low and that the patient does not have a primary defect in fatty acid or organic acid oxidation (see CLINICAL PHARMACOLOGY). In some patients, particularly those presenting with cardiomyopathy, carnitine supplementation rapidly alleviated signs and symptoms. Treatment should include, in addition to carnitine, supportive and other therapy as indicated by [...] Levocarnitine is also indicated for acute and chronic treatment of patients with an inborn error of metabolism which results in a secondary carnitine deficiency.</t>
+          <t>It Is Indicated In Patients With Chronic Constipation(Except For Constipation Associated With Organic Disease).</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Symbio Generics</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -3821,37 +3813,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:33:53</t>
-        </is>
-      </c>
-      <c r="N43" s="10" t="inlineStr">
-        <is>
-          <t>https://pdf.hres.ca/dpd_pm/00041980.PDF</t>
-        </is>
-      </c>
-      <c r="O43" s="10" t="inlineStr">
-        <is>
-          <t>https://dailymed.nlm.nih.gov/dailymed/fda/fdaDrugXsl.cfm?setid=c8a590a7-628b-45c5-ac2c-24214a69eaa6</t>
-        </is>
-      </c>
-      <c r="P43" s="10" t="inlineStr">
-        <is>
-          <t>https://dailymed.nlm.nih.gov/dailymed/fda/fdaDrugXsl.cfm?setid=c8a590a7-628b-45c5-ac2c-24214a69eaa6</t>
-        </is>
-      </c>
+          <t>01-Jul-2026 00:52</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="6" t="b">
         <v>0</v>
       </c>
@@ -3915,7 +3899,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L44" s="9" t="inlineStr">
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -3943,7 +3927,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Elobixibat Tablets 10 Mg</t>
+          <t>Levocarnitine I.P, U.S.P, E.P</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -3953,27 +3937,27 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Ferric Oxide Yellow Usp-Nf 0.0000 Not Applicable (Na),Excipients 0.0000 Q.S.,Titanium Dioxide 0.0000 Not Applicable (Na),Elobixibat Hydrate Eq. To Elobixibat 10.0000 Milligram (Mg)</t>
+          <t>Magnesium stearate, microcrystalline cellulose and povidone</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>film coated tablet</t>
+          <t>Adults: The recommended oral dosage for adults is 990 mg two or three times a day using the 330 mg tablets, depending on clinical response. Infants and children: The recommended oral dosage for infants and children is between 50 and 100 mg/kg/day in divided doses, with a maximum of 3 g/day. Dosage should begin at 50 mg/kg/day. The exact dosage will depend on clinical response.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>It Is Indicated In Patients With Chronic Constipation(Except For Constipation Associated With Organic Disease).</t>
+          <t>Levocarnitine is indicated in the treatment of primary systemic carnitine deficiency. In the reported cases, the clinical presentation consisted of recurrent episodes of Reye-like encephalopathy, hypoketotic hypoglycemia, and/or cardiomyopathy. Associated symptoms included hypotonia, muscle weakness and failure to thrive. A diagnosis of primary carnitine deficiency requires that serum, red cell and/or tissue carnitine levels be low and that the patient does not have a primary defect in fatty acid or organic acid oxidation (see CLINICAL PHARMACOLOGY). In some patients, particularly those presenting with cardiomyopathy, carnitine supplementation rapidly alleviated signs and symptoms. Treatment should include, in addition to carnitine, supportive and other therapy as indicated by [...] Levocarnitine is also indicated for acute and chronic treatment of patients with an inborn error of metabolism which results in a secondary carnitine deficiency.</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
+          <t>Symbio Generics</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -3981,29 +3965,37 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr"/>
-      <c r="O45" s="6" t="inlineStr"/>
-      <c r="P45" s="6" t="inlineStr"/>
+          <t>2026-07-08 17:33:53</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>https://pdf.hres.ca/dpd_pm/00041980.PDF</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/fda/fdaDrugXsl.cfm?setid=c8a590a7-628b-45c5-ac2c-24214a69eaa6</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/fda/fdaDrugXsl.cfm?setid=c8a590a7-628b-45c5-ac2c-24214a69eaa6</t>
+        </is>
+      </c>
       <c r="Q45" s="6" t="b">
         <v>0</v>
       </c>
@@ -4019,7 +4011,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>L-Carnitine L-Tartrate</t>
+          <t>Ribociclib Succinate</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4034,22 +4026,22 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>L-Carnitine-L-tartrate</t>
+          <t>ribociclib succinate</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Doses vary from 1,000 to 4,500 mg per day.</t>
+          <t>600 mg once daily</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>most effective for exercise performance</t>
+          <t>early breast cancer or advanced or metastatic breast cancer</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Symbio Generics</t>
+          <t>Natco Pharma Limited</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -4063,29 +4055,29 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08 17:32:22</t>
-        </is>
-      </c>
-      <c r="N46" s="9" t="inlineStr">
-        <is>
-          <t>https://www.chemspider.com/Chemical-Structure.22177977.html</t>
-        </is>
-      </c>
-      <c r="O46" s="9" t="inlineStr">
-        <is>
-          <t>https://www.healthline.com/nutrition/l-carnitine</t>
-        </is>
-      </c>
-      <c r="P46" s="9" t="inlineStr">
-        <is>
-          <t>https://www.healthline.com/nutrition/l-carnitine</t>
+          <t>2026-07-02 00:51:46</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.e-lactancia.org/media/papers/Ribociclib-DS-Novartis2023.pdf</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2017/209092s000lbl.pdf</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.oncologynewscentral.com/drugs/monograph/173394-317022/ribociclib-oral</t>
         </is>
       </c>
       <c r="Q46" s="3" t="b">
@@ -4103,7 +4095,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Ribociclib Succinate</t>
+          <t>L-Carnitine L-Tartrate</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -4118,22 +4110,22 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>ribociclib succinate</t>
+          <t>L-Carnitine-L-tartrate</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>600 mg once daily</t>
+          <t>Doses vary from 1,000 to 4,500 mg per day.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>early breast cancer or advanced or metastatic breast cancer</t>
+          <t>most effective for exercise performance</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Natco Pharma Limited</t>
+          <t>Symbio Generics</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
@@ -4147,29 +4139,29 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:51:46</t>
-        </is>
-      </c>
-      <c r="N47" s="10" t="inlineStr">
-        <is>
-          <t>https://www.e-lactancia.org/media/papers/Ribociclib-DS-Novartis2023.pdf</t>
-        </is>
-      </c>
-      <c r="O47" s="10" t="inlineStr">
-        <is>
-          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2017/209092s000lbl.pdf</t>
-        </is>
-      </c>
-      <c r="P47" s="10" t="inlineStr">
-        <is>
-          <t>https://www.oncologynewscentral.com/drugs/monograph/173394-317022/ribociclib-oral</t>
+          <t>2026-07-08 17:32:22</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.chemspider.com/Chemical-Structure.22177977.html</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.healthline.com/nutrition/l-carnitine</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.healthline.com/nutrition/l-carnitine</t>
         </is>
       </c>
       <c r="Q47" s="6" t="b">
@@ -4235,7 +4227,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L48" s="9" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -4463,7 +4455,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L51" s="10" t="inlineStr">
+      <c r="L51" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -4539,7 +4531,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L52" s="9" t="inlineStr">
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -4615,7 +4607,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L53" s="10" t="inlineStr">
+      <c r="L53" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -4691,7 +4683,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L54" s="9" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -4779,7 +4771,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L55" s="10" t="inlineStr">
+      <c r="L55" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -4807,7 +4799,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Dalbavancin Hydrochloride Bulk Drug, Dalbavancin Injection 500mg</t>
+          <t>LobeglitazoneSulfate 0.5mg+Glimepiride 1mg Tablets</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4817,7 +4809,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4832,7 +4824,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Dalbavancin for injection is indicated for the treatment of adult patients with acute bacterial skin and skin structure infections (ABSSSI), caused by susceptible isolates of the following Gram-positive microorganisms staphylococcus aureus (including methicillin susceptible and methicillin resistant strains), streptococcus pyogenes, streptococcus agalactiae, streptococcus dysgalactiae, streptococcus anginosusgroup (including S. anginosus, S. intermedius,S. constellatus) and Enterococcus faecalis (vancomycin susceptible strains).</t>
+          <t>Indicated an adjunct to diet and exercise to improve glycemic control in adults with type 2 diabetes mellitus who are already treated with a thiazolidinedione and sulphorylurea or who have inadequate glycemic control on a thiazolidinedione alone or a sulphonylurea alone.</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4872,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="R56" s="5" t="n">
-        <v>46211.74144957176</v>
+        <v>46211.74145043982</v>
       </c>
     </row>
     <row r="57">
@@ -4883,7 +4875,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>LobeglitazoneSulfate 0.5mg+Glimepiride 1mg Tablets</t>
+          <t>Dalbavancin Hydrochloride Bulk Drug, Dalbavancin Injection 500mg</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -4893,7 +4885,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -4908,7 +4900,7 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Indicated an adjunct to diet and exercise to improve glycemic control in adults with type 2 diabetes mellitus who are already treated with a thiazolidinedione and sulphorylurea or who have inadequate glycemic control on a thiazolidinedione alone or a sulphonylurea alone.</t>
+          <t>Dalbavancin for injection is indicated for the treatment of adult patients with acute bacterial skin and skin structure infections (ABSSSI), caused by susceptible isolates of the following Gram-positive microorganisms staphylococcus aureus (including methicillin susceptible and methicillin resistant strains), streptococcus pyogenes, streptococcus agalactiae, streptococcus dysgalactiae, streptococcus anginosusgroup (including S. anginosus, S. intermedius,S. constellatus) and Enterococcus faecalis (vancomycin susceptible strains).</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4948,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="R57" s="7" t="n">
-        <v>46211.74145043982</v>
+        <v>46211.74144957176</v>
       </c>
     </row>
     <row r="58">
@@ -5007,7 +4999,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr">
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -5035,7 +5027,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Semaglutide Injection 1mg/1.5ml (0.68mg/Ml), 2mg/1.5ml (1.34mg/Ml) , 4mg/3ml (1.34mg/Ml)  , 6.8mg/3ml (2.27mg/Ml), 9.6mg/3ml (3.2mg/Ml)</t>
+          <t>Relugolix</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -5045,22 +5037,22 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Semaglutide 1.0000 Mg/1 Point 5</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Initiate treatment of ORGOVYX with a loading dose of 360 mg on the first day and continue treatment with a 120 mg dose taken orally once daily at approximately the same time each day. ORGOVYX can be taken with or without food. Instruct patients to swallow tablets whole and not to crush or chew tablets. Advise patients to take a missed dose of ORGOVYX as soon as they remember. If the dose was missed by more than 12 hours, patients should not take the missed dose and resume with the next scheduled dose. If treatment with ORGOVYX is interrupted for greater than 7 days, restart ORGOVYX with a loading dose of 360 mg on the first day, and continue with a dose of 120 mg once daily.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of ? 30 Kg/M2 Or Greater (Obesity) Or ? 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
+          <t>treatment of adult patients with advanced prostate cancer.</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -5068,14 +5060,14 @@
           <t>Hetero Labs Limited</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -5083,19 +5075,31 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N59" s="6" t="inlineStr"/>
-      <c r="O59" s="6" t="inlineStr"/>
-      <c r="P59" s="6" t="inlineStr"/>
+          <t>2026-07-08 17:35:24</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2020/214621s000lbl.pdf</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.orgovyxhcp.com/dosing</t>
+        </is>
+      </c>
       <c r="Q59" s="6" t="b">
         <v>0</v>
       </c>
@@ -5106,12 +5110,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Gliclazide+Sitagliptin Phosphate Monohydrate</t>
+          <t>Semaglutide Injection 1mg/1.5ml (0.68mg/Ml), 2mg/1.5ml (1.34mg/Ml) , 4mg/3ml (1.34mg/Ml)  , 6.8mg/3ml (2.27mg/Ml), 9.6mg/3ml (3.2mg/Ml)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -5126,22 +5130,22 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Sitagliptin Phosphate Monohydrate 100.0000 Milligram (Mg),Gliclazide 30.0000 Milligram (Mg)</t>
+          <t>Semaglutide 1.0000 Mg/1 Point 5</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Injection</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus Inadequately Controlled With Metformin Monotherapy.</t>
+          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of ? 30 Kg/M2 Or Greater (Obesity) Or ? 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Eris Therapeutics Limited</t>
+          <t>Hetero Labs Limited</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -5159,7 +5163,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L60" s="9" t="inlineStr">
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -5187,7 +5191,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Caffeine (Anhydrous)+Paracetamol+Propyphenazone</t>
+          <t>Gliclazide+Sitagliptin Phosphate Monohydrate</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -5202,7 +5206,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Paracetamol 250.0000 Milligram (Mg),Propyphenazone 150.0000 Milligram (Mg),Caffeine (Anhydrous) 30.0000 Milligram (Mg)</t>
+          <t>Sitagliptin Phosphate Monohydrate 100.0000 Milligram (Mg),Gliclazide 30.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -5212,12 +5216,12 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Mild To Moderate Headache</t>
+          <t>Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus Inadequately Controlled With Metformin Monotherapy.</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>JAGDALE INDUSTRIES PRIVATE LIMITED (JUGGAT PHARMA- PHARMA DIVISION)</t>
+          <t>Eris Therapeutics Limited</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -5235,7 +5239,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="L61" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -5258,12 +5262,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Respiratory Syncytial Virus (Rsv) Vaccine (Recombinant, Adjuvanted)</t>
+          <t>Caffeine (Anhydrous)+Paracetamol+Propyphenazone</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -5278,22 +5282,22 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Rsvpref3 Antigen 120.0000 Micrograms (?g),Trehalose Dihydrate 14.7000 Milligram (Mg),Polysorbate 80 (Ps80) 0.1800 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.2900 Milligram (Mg),Dipotassium Phosphate (K2hpo4) 0.2600 Milligram (Mg),3-O-Desacyl-4?- Monophosphoryl Lipid A (Mpl) 25.0000 Micrograms (?g),Purified Quillaja Saponin (Qs-21) 25.0000 Micrograms (?g),Dioleoyl Phosphatidylcholine (Dopc) 500.0000 Micrograms (?g),Cholesterol 125.0000 Micrograms (?g),Sodium Chloride (Nacl) 4.4000 Milligram (Mg),Disodium Phosphate Anhydrous (Na2hpo4) 0.1500 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.5400 Milligram (Mg),Water For Injection (Wfi) Q.S Ad 0.5000 Ml</t>
+          <t>Paracetamol 250.0000 Milligram (Mg),Propyphenazone 150.0000 Milligram (Mg),Caffeine (Anhydrous) 30.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Powder and suspension for suspension for injection</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Arexvy Is Indicated For Active Immunisation For The Prevention Of Lower Respiratory Tract Disease (Lrtd) Caused By Respiratory Syncytial Virus In: ?	Adults 60 Years Of Age And Older; ?	Adults 50 Through 59 Years Of Age Who Are At Increased Risk For Rsv Disease.</t>
+          <t>Mild To Moderate Headache</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>GLAXOSMITHKLINE PHARMACEUTICALS LIMITED</t>
+          <t>JAGDALE INDUSTRIES PRIVATE LIMITED (JUGGAT PHARMA- PHARMA DIVISION)</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -5311,7 +5315,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L62" s="9" t="inlineStr">
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -5334,12 +5338,12 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Relugolix</t>
+          <t>Respiratory Syncytial Virus (Rsv) Vaccine (Recombinant, Adjuvanted)</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -5349,37 +5353,37 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Rsvpref3 Antigen 120.0000 Micrograms (?g),Trehalose Dihydrate 14.7000 Milligram (Mg),Polysorbate 80 (Ps80) 0.1800 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.2900 Milligram (Mg),Dipotassium Phosphate (K2hpo4) 0.2600 Milligram (Mg),3-O-Desacyl-4?- Monophosphoryl Lipid A (Mpl) 25.0000 Micrograms (?g),Purified Quillaja Saponin (Qs-21) 25.0000 Micrograms (?g),Dioleoyl Phosphatidylcholine (Dopc) 500.0000 Micrograms (?g),Cholesterol 125.0000 Micrograms (?g),Sodium Chloride (Nacl) 4.4000 Milligram (Mg),Disodium Phosphate Anhydrous (Na2hpo4) 0.1500 Milligram (Mg),Potassium Dihydrogen Phosphate (Kh2po4) 0.5400 Milligram (Mg),Water For Injection (Wfi) Q.S Ad 0.5000 Ml</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Initiate treatment of ORGOVYX with a loading dose of 360 mg on the first day and continue treatment with a 120 mg dose taken orally once daily at approximately the same time each day. ORGOVYX can be taken with or without food. Instruct patients to swallow tablets whole and not to crush or chew tablets. Advise patients to take a missed dose of ORGOVYX as soon as they remember. If the dose was missed by more than 12 hours, patients should not take the missed dose and resume with the next scheduled dose. If treatment with ORGOVYX is interrupted for greater than 7 days, restart ORGOVYX with a loading dose of 360 mg on the first day, and continue with a dose of 120 mg once daily.</t>
+          <t>Powder and suspension for suspension for injection</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>treatment of adult patients with advanced prostate cancer.</t>
+          <t>Arexvy Is Indicated For Active Immunisation For The Prevention Of Lower Respiratory Tract Disease (Lrtd) Caused By Respiratory Syncytial Virus In: ?	Adults 60 Years Of Age And Older; ?	Adults 50 Through 59 Years Of Age Who Are At Increased Risk For Rsv Disease.</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>GLAXOSMITHKLINE PHARMACEUTICALS LIMITED</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>composition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -5387,31 +5391,19 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:35:24</t>
-        </is>
-      </c>
-      <c r="N63" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="O63" s="10" t="inlineStr">
-        <is>
-          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2020/214621s000lbl.pdf</t>
-        </is>
-      </c>
-      <c r="P63" s="10" t="inlineStr">
-        <is>
-          <t>https://www.orgovyxhcp.com/dosing</t>
-        </is>
-      </c>
+          <t>01-Jul-2026 00:52</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr"/>
+      <c r="P63" s="6" t="inlineStr"/>
       <c r="Q63" s="6" t="b">
         <v>0</v>
       </c>
@@ -5475,7 +5467,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L64" s="9" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -5855,7 +5847,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L69" s="10" t="inlineStr">
+      <c r="L69" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -5931,7 +5923,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L70" s="9" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -7299,7 +7291,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L88" s="9" t="inlineStr">
+      <c r="L88" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -7319,7 +7311,7 @@
           <t>Not Available</t>
         </is>
       </c>
-      <c r="P88" s="9" t="inlineStr">
+      <c r="P88" s="3" t="inlineStr">
         <is>
           <t>https://edaegypt.gov.eg/media/wkncjefo/par-adsorbed-tetanus.pdf</t>
         </is>
@@ -7387,7 +7379,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L89" s="10" t="inlineStr">
+      <c r="L89" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -7397,7 +7389,7 @@
           <t>2026-07-08 17:32:53</t>
         </is>
       </c>
-      <c r="N89" s="10" t="inlineStr">
+      <c r="N89" s="6" t="inlineStr">
         <is>
           <t>https://www.edaegypt.gov.eg/media/kwmbcnoj/betd_par.pdf</t>
         </is>
@@ -7627,7 +7619,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L92" s="9" t="inlineStr">
+      <c r="L92" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -7779,7 +7771,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L94" s="9" t="inlineStr">
+      <c r="L94" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -7878,12 +7870,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
+          <t>Semaglutide Injection</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -7898,22 +7890,22 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Filamentous Haemagglutinin 25.0000 Micrograms (?g),Tetanus Toxoid 40.0000 Iu,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 Du,Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 Du,Pertussis Toxoid 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 Du,Diphtheria Toxoid 30.0000 Iu</t>
+          <t>Semaglutide 0.2500 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Suspension for injection in a prefilled syringe</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>"This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations"</t>
+          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of - ?	30 Kg/M2 Or Greater (Obesity) Or ?	27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -7931,7 +7923,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L96" s="9" t="inlineStr">
+      <c r="L96" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -7954,12 +7946,12 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Mirvetuximab Soravtansine Injection 5mg/Ml</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -7969,37 +7961,37 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>Mirvetuximab Soravtansine 5.0000 Mg/Ml,Acetic Acid, Glacial 0.2200 Mg/Ml,Polysorbate 20 0.1000 Mg/Ml,Sodium Acetate, Anhydrous 0.5300 Mg/Ml,Sucrose 90.0000 Mg/Ml,Water For Injection 1.0000 Ml</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Adults—At first, 0.25 milligrams (mg) injected under the skin once a week for 4 weeks. Your doctor may increase your dose as needed.</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Elahere As Monotherapy Is Indicated For The Treatment Of Adult Patients With Folate Receptor-Alpha (Fr?) Positive, Platinum-Resistant Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer, Who Have Received One To Three Prior Systemic Treatment Regimens.</t>
+          <t>Indicated for non-cirrhotic metabolic dysfunction-associated steatohepatitis (MASH) with moderate or advanced liver fibrosis (stage F2 or F3); as an adjunct to diet and exercise to improve glycemic control in adults with type 2 diabetes; and to reduce the risk of major adverse cardiovascular events in adults with type 2 diabetes and established cardiovascular disease.</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>AbbVie Healthcare India Private Limited</t>
-        </is>
-      </c>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>M/s. VXL Life Sciences</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -8007,19 +7999,31 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L97" s="10" t="inlineStr">
+      <c r="L97" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N97" s="6" t="inlineStr"/>
-      <c r="O97" s="6" t="inlineStr"/>
-      <c r="P97" s="6" t="inlineStr"/>
+          <t>2026-07-08 17:35:30</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mayoclinic.org/drugs-supplements/semaglutide-subcutaneous-route/description/drg-20406730</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semaglutide</t>
+        </is>
+      </c>
       <c r="Q97" s="6" t="b">
         <v>0</v>
       </c>
@@ -8030,12 +8034,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Tegoprazan</t>
+          <t>Enfortumab Vedotin</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -8050,22 +8054,22 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Ferric Oxide Red Usp Nf 0.0000 Q.S.,Titanium Dioxide 0.0000 Q.S.,Excipients 0.0000 Q.S.,Ferric Oxide Black Usp Nf 0.0000 Q.S.,Tegoprazan 25.0000 Milligram (Mg)</t>
+          <t>Enfortumab Vedotin, 20.0000 Milligram (Mg),Polysorbate 20, Nf, Jpe 0.4000 Milligram (Mg),Histidine Hydrochloride Monohydrate 4.6200 Milligram (Mg),Trehalose Dihydrate, Nf 110.0000 Milligram (Mg),Histidine 2.8000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Film coated tablet</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Tegoprazan Tablets 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease.,Tegoprazan Tablets 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non-Erosive Gastroesophageal Reflux Disease, Gastric Ulcer</t>
+          <t>Padcev, In Combination With Pembrolizumab, Is Indicated For The Treatment Of Adult Patients With Locally Advanced Or Metastatic Urothelial Cancer (Muc).</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
+          <t>Astellas Pharma India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -8083,7 +8087,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L98" s="9" t="inlineStr">
+      <c r="L98" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -8106,12 +8110,12 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Enfortumab Vedotin</t>
+          <t>Tegoprazan</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -8126,22 +8130,22 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Enfortumab Vedotin, 20.0000 Milligram (Mg),Polysorbate 20, Nf, Jpe 0.4000 Milligram (Mg),Histidine Hydrochloride Monohydrate 4.6200 Milligram (Mg),Trehalose Dihydrate, Nf 110.0000 Milligram (Mg),Histidine 2.8000 Milligram (Mg)</t>
+          <t>Ferric Oxide Red Usp Nf 0.0000 Q.S.,Titanium Dioxide 0.0000 Q.S.,Excipients 0.0000 Q.S.,Ferric Oxide Black Usp Nf 0.0000 Q.S.,Tegoprazan 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>Film coated tablet</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Padcev, In Combination With Pembrolizumab, Is Indicated For The Treatment Of Adult Patients With Locally Advanced Or Metastatic Urothelial Cancer (Muc).</t>
+          <t>Tegoprazan Tablets 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease.,Tegoprazan Tablets 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non-Erosive Gastroesophageal Reflux Disease, Gastric Ulcer</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>Astellas Pharma India Pvt. Ltd.</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
@@ -8159,7 +8163,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L99" s="10" t="inlineStr">
+      <c r="L99" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -8182,12 +8186,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Vonoprazan Tablets</t>
+          <t>Mirvetuximab Soravtansine Injection 5mg/Ml</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -8202,22 +8206,22 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Vonoprazan Fumarate Eq. To Vonoprazan 10.0000 Milligram (Mg)</t>
+          <t>Mirvetuximab Soravtansine 5.0000 Mg/Ml,Acetic Acid, Glacial 0.2200 Mg/Ml,Polysorbate 20 0.1000 Mg/Ml,Sodium Acetate, Anhydrous 0.5300 Mg/Ml,Sucrose 90.0000 Mg/Ml,Water For Injection 1.0000 Ml</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Treatment Of Reflux Esophagitis(Re) , Treatment Of Gastric Ulcer (Gu) , Treatment Of Duodenal Ulcer(Du) , Prevention Of Recurrence Of Gastric Ulcer Or Duodenal Ulcer During Low-Dose Aspirin Administration. , Prevention Of Recurrence Of Gastric Ulcer Or Duodenal Ulcer During Nsaids Administration. , Adjunct To Helicobacter Pylori Eradication Associated With: Gastric Ulcer, Duodenal Ulcer, Gastric Malt Lymphoma, Idiopathic Thrombocytopenic Purpura, The Stomach After Endoscopic Resection Of Early-Stage Cancer, Or Helicobacter Pylori Gastritis.</t>
+          <t>Elahere As Monotherapy Is Indicated For The Treatment Of Adult Patients With Folate Receptor-Alpha (Fr?) Positive, Platinum-Resistant Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer, Who Have Received One To Three Prior Systemic Treatment Regimens.</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Saitech Medicare Pvt. Ltd</t>
+          <t>AbbVie Healthcare India Private Limited</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -8235,7 +8239,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L100" s="9" t="inlineStr">
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -8258,12 +8262,12 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -8273,37 +8277,37 @@
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Filamentous Haemagglutinin 25.0000 Micrograms (?g),Tetanus Toxoid 40.0000 Iu,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 Du,Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 Du,Pertussis Toxoid 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 Du,Diphtheria Toxoid 30.0000 Iu</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Adults—At first, 0.25 milligrams (mg) injected under the skin once a week for 4 weeks. Your doctor may increase your dose as needed.</t>
+          <t>Suspension for injection in a prefilled syringe</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Indicated for non-cirrhotic metabolic dysfunction-associated steatohepatitis (MASH) with moderate or advanced liver fibrosis (stage F2 or F3); as an adjunct to diet and exercise to improve glycemic control in adults with type 2 diabetes; and to reduce the risk of major adverse cardiovascular events in adults with type 2 diabetes and established cardiovascular disease.</t>
+          <t>"This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations"</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>M/s. VXL Life Sciences</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>composition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
@@ -8311,31 +8315,19 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L101" s="10" t="inlineStr">
+      <c r="L101" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:35:30</t>
-        </is>
-      </c>
-      <c r="N101" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="O101" s="10" t="inlineStr">
-        <is>
-          <t>https://www.mayoclinic.org/drugs-supplements/semaglutide-subcutaneous-route/description/drg-20406730</t>
-        </is>
-      </c>
-      <c r="P101" s="10" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Semaglutide</t>
-        </is>
-      </c>
+          <t>01-Jul-2026 00:52</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr"/>
+      <c r="O101" s="6" t="inlineStr"/>
+      <c r="P101" s="6" t="inlineStr"/>
       <c r="Q101" s="6" t="b">
         <v>0</v>
       </c>
@@ -8351,7 +8343,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Semaglutide Injection</t>
+          <t>Vonoprazan Tablets</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -8366,22 +8358,22 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Semaglutide 0.2500 Milligram (Mg)</t>
+          <t>Vonoprazan Fumarate Eq. To Vonoprazan 10.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of - ?	30 Kg/M2 Or Greater (Obesity) Or ?	27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia)</t>
+          <t>Treatment Of Reflux Esophagitis(Re) , Treatment Of Gastric Ulcer (Gu) , Treatment Of Duodenal Ulcer(Du) , Prevention Of Recurrence Of Gastric Ulcer Or Duodenal Ulcer During Low-Dose Aspirin Administration. , Prevention Of Recurrence Of Gastric Ulcer Or Duodenal Ulcer During Nsaids Administration. , Adjunct To Helicobacter Pylori Eradication Associated With: Gastric Ulcer, Duodenal Ulcer, Gastric Malt Lymphoma, Idiopathic Thrombocytopenic Purpura, The Stomach After Endoscopic Resection Of Early-Stage Cancer, Or Helicobacter Pylori Gastritis.</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Saitech Medicare Pvt. Ltd</t>
         </is>
       </c>
       <c r="I102" s="8" t="inlineStr">
@@ -8399,7 +8391,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L102" s="9" t="inlineStr">
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -8498,12 +8490,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Avibactam (As Sodium Salt) 0.5 Gm+Aztreonam 1.5 Gm</t>
+          <t>Insulin Injection, Soluble (Neutral) Ip 100iu/Ml</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -8518,22 +8510,22 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Avibactam (As Sodium Salt)0.5 Gm 0.5000 Gram (G)</t>
+          <t>Glycerol 16.0000 Mg/Ml,Water For Injection 1.0000 Q.S.,Hydrochloric Acid 1.0000 Q.S. To Adjust Ph,Metacresol 2.5000 Mg/Ml,Sodium Hydroxide 1.0000 Q.S. To Adjust Ph,Human Insulin (Rdna Origin) 100.0000 Iu/Ml</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Solution for infusion</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Complicated Intra-Abdominal Infection (Ciai),Hospital-Acquired Pneumonia (Hap), Including Ventilator-Associated Pneumonia (Vap),Complicated Urinary Tract Infection (Cuti), Including Pyelonephritis.,Treatment Of Infections Due To Aerobic Gram-Negative Organism?S In Adult Patients With Limited Treatment Options.</t>
+          <t>Diabetes Type I And Type Ii</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>GUFIC BIOSCIENCES LIMITED</t>
+          <t>Regenix Drugs Ltd.</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
@@ -8551,7 +8543,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L104" s="9" t="inlineStr">
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -8574,12 +8566,12 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Human Insulin (Rdna Origin)</t>
+          <t>Avibactam (As Sodium Salt) 0.5 Gm+Aztreonam 1.5 Gm</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -8589,27 +8581,27 @@
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Each ml contains: Insulin Human I.P. 100 IU (Human Insulin of rDNA Origin)</t>
+          <t>Avibactam (As Sodium Salt)0.5 Gm 0.5000 Gram (G)</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Dosage is individual and determined in accordance with the needs of the patient. The individual insulin requirement is usually between 0.3 and 1.0 IU/kg/day.</t>
+          <t>Solution for infusion</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>Treatment of diabetes mellitus.</t>
+          <t>Complicated Intra-Abdominal Infection (Ciai),Hospital-Acquired Pneumonia (Hap), Including Ventilator-Associated Pneumonia (Vap),Complicated Urinary Tract Infection (Cuti), Including Pyelonephritis.,Treatment Of Infections Due To Aerobic Gram-Negative Organism?S In Adult Patients With Limited Treatment Options.</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>Regenix Drugs Ltd.</t>
+          <t>GUFIC BIOSCIENCES LIMITED</t>
         </is>
       </c>
       <c r="I105" s="8" t="inlineStr">
@@ -8617,37 +8609,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J105" s="6" t="inlineStr"/>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L105" s="10" t="inlineStr">
+      <c r="L105" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:55:21</t>
-        </is>
-      </c>
-      <c r="N105" s="10" t="inlineStr">
-        <is>
-          <t>https://www.sanofi.com/assets/countries/india/docs/science-and-innovation/for-healthcare-profsionals/product-information/pharmaceuticals/insutage-pi.pdf</t>
-        </is>
-      </c>
-      <c r="O105" s="10" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/health/documents/community-register/2009/2009100164888/anx_64888_en.pdf</t>
-        </is>
-      </c>
-      <c r="P105" s="10" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/health/documents/community-register/2009/2009100164888/anx_64888_en.pdf</t>
-        </is>
-      </c>
+          <t>01-Jul-2026 00:52</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr"/>
+      <c r="O105" s="6" t="inlineStr"/>
+      <c r="P105" s="6" t="inlineStr"/>
       <c r="Q105" s="6" t="b">
         <v>0</v>
       </c>
@@ -8663,7 +8647,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Insulin Injection, Soluble (Neutral) Ip 100iu/Ml</t>
+          <t>Human Insulin (Rdna Origin)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -8673,22 +8657,22 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Glycerol 16.0000 Mg/Ml,Water For Injection 1.0000 Q.S.,Hydrochloric Acid 1.0000 Q.S. To Adjust Ph,Metacresol 2.5000 Mg/Ml,Sodium Hydroxide 1.0000 Q.S. To Adjust Ph,Human Insulin (Rdna Origin) 100.0000 Iu/Ml</t>
+          <t>Each ml contains: Insulin Human I.P. 100 IU (Human Insulin of rDNA Origin)</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Dosage is individual and determined in accordance with the needs of the patient. The individual insulin requirement is usually between 0.3 and 1.0 IU/kg/day.</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Diabetes Type I And Type Ii</t>
+          <t>Treatment of diabetes mellitus.</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
@@ -8701,29 +8685,37 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J106" s="3" t="inlineStr"/>
       <c r="K106" s="3" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L106" s="9" t="inlineStr">
+      <c r="L106" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="inlineStr"/>
-      <c r="O106" s="3" t="inlineStr"/>
-      <c r="P106" s="3" t="inlineStr"/>
+          <t>2026-07-02 00:55:21</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sanofi.com/assets/countries/india/docs/science-and-innovation/for-healthcare-profsionals/product-information/pharmaceuticals/insutage-pi.pdf</t>
+        </is>
+      </c>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/health/documents/community-register/2009/2009100164888/anx_64888_en.pdf</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/health/documents/community-register/2009/2009100164888/anx_64888_en.pdf</t>
+        </is>
+      </c>
       <c r="Q106" s="3" t="b">
         <v>0</v>
       </c>
@@ -8734,12 +8726,12 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Insulin Glargine Injection</t>
+          <t>Micronized Purified Flavonoid Fraction 500 Mg Tablets</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -8754,22 +8746,23 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Insulin Glargine 100.0000 Iu/Ml,Sodium Hydroxide 0.0000 Q.S,M-Cresol 2.7000 Milligram (Mg),Glycerol (85%) 20.0000 Milligram (Mg),Zinc* (As Zinc Chloride) 30.0000 Micrograms (?g),Hydrochloric Acid 0.0000 Q.S,Water For Injection 0.0000 Q.S To 1 Ml</t>
+          <t>Micronized Purified Flavonoid Fraction 500.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Or Above With Diabetes Mellitus, Where Treatment With Insulin Is Required</t>
+          <t>1. Treatment Of Symptoms Related To Venolymphatic Insufficiency (Heavy Legs Pain, Restless Legs Syndrome).
+2.Treatment Of Functional Symptoms Related To Hemorrhoidal Attack.</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>Biocon Biologics Limited</t>
+          <t>SERVIER INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I107" s="8" t="inlineStr">
@@ -8787,7 +8780,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L107" s="10" t="inlineStr">
+      <c r="L107" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -8815,7 +8808,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
+          <t>Insulin Glargine Injection</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -8830,22 +8823,22 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Diphtheria Toxoid 20.0000 Iu (30 Lf),Tetanus Toxoid 40.0000 Iu (10 Lf),Bordetella Pertussis Antigens- Pertussis Toxoid 25.0000 Micrograms (?g),Bordetella Pertussis Antigens- Filamentous Haemagglutinin 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 D Antigen Units,Aluminium Hydroxide, Hydrated 0.3000 Mg Al,Phenoxyethanol - Ethanol (50 % V/V Solution) Phenoxyethanol 2.5000 ?l,Phenoxyethanol - Ethanol (50 % V/V Solution) Ethanol Anhydrous 2.5000 ?l,Formaldehyde Solution 10.0000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0500 Ml,Water For Injections 0.0000 Upto 0.5 Ml</t>
+          <t>Insulin Glargine 100.0000 Iu/Ml,Sodium Hydroxide 0.0000 Q.S,M-Cresol 2.7000 Milligram (Mg),Glycerol (85%) 20.0000 Milligram (Mg),Zinc* (As Zinc Chloride) 30.0000 Micrograms (?g),Hydrochloric Acid 0.0000 Q.S,Water For Injection 0.0000 Q.S To 1 Ml</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Suspension for injection in a prefilled syringe</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations</t>
+          <t>For The Treatment Of Adults, Adolescents And Children Of 2 Years Or Above With Diabetes Mellitus, Where Treatment With Insulin Is Required</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+          <t>Biocon Biologics Limited</t>
         </is>
       </c>
       <c r="I108" s="8" t="inlineStr">
@@ -8863,7 +8856,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L108" s="9" t="inlineStr">
+      <c r="L108" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -8891,7 +8884,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Micronized Purified Flavonoid Fraction 500 Mg Tablets</t>
+          <t>Edoxaban Tosylate Monohydrate Bulk Drug</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -8901,28 +8894,27 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>Micronized Purified Flavonoid Fraction 500.0000 Milligram (Mg)</t>
+          <t>Edoxaban Tosylate Monohydrate</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>60 mg, 1 times / day Route: oral</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>1. Treatment Of Symptoms Related To Venolymphatic Insufficiency (Heavy Legs Pain, Restless Legs Syndrome).
-2.Treatment Of Functional Symptoms Related To Hemorrhoidal Attack.</t>
+          <t>to reduce the risk of stroke and systemic embolism (SE) in patients with nonvalvular atrial fibrillation (NVAF).</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>SERVIER INDIA PRIVATE LIMITED</t>
+          <t>M/s. MSN Life Sciences Private Limited</t>
         </is>
       </c>
       <c r="I109" s="8" t="inlineStr">
@@ -8930,29 +8922,37 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J109" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J109" s="6" t="inlineStr"/>
       <c r="K109" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L109" s="10" t="inlineStr">
+      <c r="L109" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N109" s="6" t="inlineStr"/>
-      <c r="O109" s="6" t="inlineStr"/>
-      <c r="P109" s="6" t="inlineStr"/>
+          <t>2026-07-02 00:52:06</t>
+        </is>
+      </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>https://ndclist.com/active-ingredients/edoxaban-tosylate-monohydrate</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>https://drugs.ncats.io/drug/972203R4EW</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>https://drugs.ncats.io/drug/972203R4EW</t>
+        </is>
+      </c>
       <c r="Q109" s="6" t="b">
         <v>0</v>
       </c>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Edoxaban Tosylate Monohydrate Bulk Drug</t>
+          <t>Ertapenem Sodium</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -8983,22 +8983,22 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Edoxaban Tosylate Monohydrate</t>
+          <t>Poudre pour solution 1 g d’ertapénem/flacon (sous forme d’ertapénem monosodique). Ingrédients non médicinaux: Hydrogénocarbonate de sodium et hydroxyde de sodium.</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>60 mg, 1 times / day Route: oral</t>
+          <t>Adult patients with severe renal impairment (creatinine clearance ≤30 mL/min/1.73 m2) and end-stage renal disease (creatinine clearance ≤10 mL/min/1.73 m2) should receive 500 mg daily. A supplementary dose of 150 mg is recommended if ertapenem is administered within 6 hours prior to hemodialysis.</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>to reduce the risk of stroke and systemic embolism (SE) in patients with nonvalvular atrial fibrillation (NVAF).</t>
+          <t>Complicated Intra-Abdominal Infections; Complicated Skin and Skin Structure Infections, Including Diabetic Foot Infections without Osteomyelitis; Community Acquired Pneumonia; Complicated Urinary Tract Infections Including Pyelonephritis; Acute Pelvic Infections Including Postpartum Endomyometritis, Septic Abortion and Post-Surgical Gynecologic Infections; Prophylaxis of Surgical Site Infection Following Elective Colorectal Surgery.</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>M/s. MSN Life Sciences Private Limited</t>
+          <t>DIVINNE SBR INTERNATIONAL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr">
@@ -9012,29 +9012,29 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L110" s="9" t="inlineStr">
+      <c r="L110" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02 00:52:06</t>
-        </is>
-      </c>
-      <c r="N110" s="9" t="inlineStr">
-        <is>
-          <t>https://ndclist.com/active-ingredients/edoxaban-tosylate-monohydrate</t>
-        </is>
-      </c>
-      <c r="O110" s="9" t="inlineStr">
-        <is>
-          <t>https://drugs.ncats.io/drug/972203R4EW</t>
-        </is>
-      </c>
-      <c r="P110" s="9" t="inlineStr">
-        <is>
-          <t>https://drugs.ncats.io/drug/972203R4EW</t>
+          <t>2026-07-02 00:52:27</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.hres.ca/dpd_pm/00070374.PDF</t>
+        </is>
+      </c>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/drugInfo.cfm?setid=f74cca2f-e775-4580-acae-3a0c47dd24d9</t>
+        </is>
+      </c>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>https://dailymed.nlm.nih.gov/dailymed/drugInfo.cfm?setid=f74cca2f-e775-4580-acae-3a0c47dd24d9</t>
         </is>
       </c>
       <c r="Q110" s="3" t="b">
@@ -9047,12 +9047,12 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Ertapenem Sodium</t>
+          <t>Adsorbed Diphtheria, Tetanus, Pertussis (Acellular Component) And Inactivated Poliomyelitis Vaccine I.P.</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -9062,27 +9062,27 @@
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>Poudre pour solution 1 g d’ertapénem/flacon (sous forme d’ertapénem monosodique). Ingrédients non médicinaux: Hydrogénocarbonate de sodium et hydroxyde de sodium.</t>
+          <t>Diphtheria Toxoid 20.0000 Iu (30 Lf),Tetanus Toxoid 40.0000 Iu (10 Lf),Bordetella Pertussis Antigens- Pertussis Toxoid 25.0000 Micrograms (?g),Bordetella Pertussis Antigens- Filamentous Haemagglutinin 25.0000 Micrograms (?g),Poliomyelitis Virus (Inactivated) Type 1 (Mahoney Strain) 29.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 2 (Mef-1 Strain) 7.0000 D Antigen Units,Poliomyelitis Virus (Inactivated) Type 3 (Saukett Strain) 26.0000 D Antigen Units,Aluminium Hydroxide, Hydrated 0.3000 Mg Al,Phenoxyethanol - Ethanol (50 % V/V Solution) Phenoxyethanol 2.5000 ?l,Phenoxyethanol - Ethanol (50 % V/V Solution) Ethanol Anhydrous 2.5000 ?l,Formaldehyde Solution 10.0000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0500 Ml,Water For Injections 0.0000 Upto 0.5 Ml</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>Adult patients with severe renal impairment (creatinine clearance ≤30 mL/min/1.73 m2) and end-stage renal disease (creatinine clearance ≤10 mL/min/1.73 m2) should receive 500 mg daily. A supplementary dose of 150 mg is recommended if ertapenem is administered within 6 hours prior to hemodialysis.</t>
+          <t>Suspension for injection in a prefilled syringe</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>Complicated Intra-Abdominal Infections; Complicated Skin and Skin Structure Infections, Including Diabetic Foot Infections without Osteomyelitis; Community Acquired Pneumonia; Complicated Urinary Tract Infections Including Pyelonephritis; Acute Pelvic Infections Including Postpartum Endomyometritis, Septic Abortion and Post-Surgical Gynecologic Infections; Prophylaxis of Surgical Site Infection Following Elective Colorectal Surgery.</t>
+          <t>This Vaccine Is Indicated In The Joint Prevention Of Diphtheria, Tetanus, Pertussis And Poliomyelitis: ? For Primary Vaccination In Infants From The Age Of 6 Weeks, ? For Booster Vaccination, One Year After Primary Vaccination During The Second Year Of Life, ? For Booster Vaccination Between 4 And 13 Years Of Age, According To Official Recommendations</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>DIVINNE SBR INTERNATIONAL PRIVATE LIMITED</t>
+          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr">
@@ -9090,37 +9090,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J111" s="6" t="inlineStr"/>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L111" s="10" t="inlineStr">
+      <c r="L111" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:52:27</t>
-        </is>
-      </c>
-      <c r="N111" s="10" t="inlineStr">
-        <is>
-          <t>https://pdf.hres.ca/dpd_pm/00070374.PDF</t>
-        </is>
-      </c>
-      <c r="O111" s="10" t="inlineStr">
-        <is>
-          <t>https://dailymed.nlm.nih.gov/dailymed/drugInfo.cfm?setid=f74cca2f-e775-4580-acae-3a0c47dd24d9</t>
-        </is>
-      </c>
-      <c r="P111" s="10" t="inlineStr">
-        <is>
-          <t>https://dailymed.nlm.nih.gov/dailymed/drugInfo.cfm?setid=f74cca2f-e775-4580-acae-3a0c47dd24d9</t>
-        </is>
-      </c>
+          <t>01-Jul-2026 00:52</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr"/>
+      <c r="O111" s="6" t="inlineStr"/>
+      <c r="P111" s="6" t="inlineStr"/>
       <c r="Q111" s="6" t="b">
         <v>0</v>
       </c>
@@ -9283,12 +9275,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Abiraterone Acetate Tablets Ip</t>
+          <t>Guselkumab</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -9303,22 +9295,22 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Abiraterone Acetate 1000.0000 Milligram (Mg)</t>
+          <t>L-Histidine Monohydrochloride Monohydrate 26.6000 Milligram (Mg),L-Methionine 8.0000 Milligram (Mg),Polysorbate 80 10.0000 Milligram (Mg),L-Histidine 11.3000 Milligram (Mg),Edta-Disodium Dihydrate 0.4000 Milligram (Mg),Guselkumab 200.0000 Milligram (Mg),Water For Injection 20.0000 Ml,Sucrose 1700.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Solution for injection, Solution for infusion</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>For The Treatment Of 1) In Combination With Prednisone For The Treatment Of Patients With Metastatic Castration-Resistant Prostate Cancer Who Have Received Prior Chemotherapy Containing Docetaxel. 2) Indicated For The Treatment Of Metastatic Castration Resistant Prostate Cancer In Adult Men Who Are Asymptomatic Or Mildly Symptomatic After Failure Of Androgen Deprivation Therapy In Whom Chemotherapy Is Not Yet Clinically Indicated, With Prednisone Or Prednisolone.</t>
+          <t>Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Ulcerative Colitis,Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Crohn?S Disease</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>MSN Laboratories Private Limited</t>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
@@ -9336,7 +9328,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L114" s="9" t="inlineStr">
+      <c r="L114" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -9359,12 +9351,12 @@
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Belumosudil Mesylate-Bulk Drug</t>
+          <t>Inactivated Poliomyelitis Vaccine I.P.</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -9374,37 +9366,37 @@
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 1 (Mahoney) 29.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 2 (Mef) 7.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 3 (Saukett) 26.0000 D Antigen Units,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Phenoxyethanol 2.5000 ?l,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Ethanol 2.5000 ?l,Formaldehyde Solution 12.5000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0000 Q.S. To 0.5 Ml</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>The recommended dose of REZUROCK is 200 mg given orally once daily until progression of chronic GVHD that requires new systemic therapy.</t>
+          <t>Suspension for injection</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>REZUROCK is indicated for the treatment of adult and pediatric patients 12 years and older with chronic graft-versus-host disease (chronic GVHD) after failure of at least two prior lines of systemic therapy.</t>
+          <t>Active Immunization Of Infants, Children And Adults For Prevention Of Poliomyelitis</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>MSN Organics Private Limited</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>composition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
@@ -9412,27 +9404,19 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L115" s="10" t="inlineStr">
+      <c r="L115" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:33:33</t>
+          <t>01-Jul-2026 00:52</t>
         </is>
       </c>
       <c r="N115" s="6" t="inlineStr"/>
-      <c r="O115" s="10" t="inlineStr">
-        <is>
-          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2021/214783s000lbl.pdf</t>
-        </is>
-      </c>
-      <c r="P115" s="10" t="inlineStr">
-        <is>
-          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2021/214783s000lbl.pdf</t>
-        </is>
-      </c>
+      <c r="O115" s="6" t="inlineStr"/>
+      <c r="P115" s="6" t="inlineStr"/>
       <c r="Q115" s="6" t="b">
         <v>0</v>
       </c>
@@ -9443,12 +9427,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Bevacizumab</t>
+          <t>Dapagliflozin+Metoprolol Sr</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -9463,22 +9447,22 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Bevacizumab 100.0000 Mg/4ml (25 Mg/Ml)</t>
+          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Metoprolol Succinate 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Concentrate solution for infusion</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Hepatocellular Carcinoma (Hcc)</t>
+          <t>Heart Failure Post-Acute Myocardial Infarction</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Limited</t>
+          <t>Eris Lifesciences Limited</t>
         </is>
       </c>
       <c r="I116" s="8" t="inlineStr">
@@ -9496,7 +9480,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L116" s="9" t="inlineStr">
+      <c r="L116" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -9519,12 +9503,12 @@
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Guselkumab</t>
+          <t>Abiraterone Acetate Tablets Ip</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -9539,22 +9523,22 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>L-Histidine Monohydrochloride Monohydrate 26.6000 Milligram (Mg),L-Methionine 8.0000 Milligram (Mg),Polysorbate 80 10.0000 Milligram (Mg),L-Histidine 11.3000 Milligram (Mg),Edta-Disodium Dihydrate 0.4000 Milligram (Mg),Guselkumab 200.0000 Milligram (Mg),Water For Injection 20.0000 Ml,Sucrose 1700.0000 Milligram (Mg)</t>
+          <t>Abiraterone Acetate 1000.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Solution for injection, Solution for infusion</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Ulcerative Colitis,Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Crohn?S Disease</t>
+          <t>For The Treatment Of 1) In Combination With Prednisone For The Treatment Of Patients With Metastatic Castration-Resistant Prostate Cancer Who Have Received Prior Chemotherapy Containing Docetaxel. 2) Indicated For The Treatment Of Metastatic Castration Resistant Prostate Cancer In Adult Men Who Are Asymptomatic Or Mildly Symptomatic After Failure Of Androgen Deprivation Therapy In Whom Chemotherapy Is Not Yet Clinically Indicated, With Prednisone Or Prednisolone.</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
+          <t>MSN Laboratories Private Limited</t>
         </is>
       </c>
       <c r="I117" s="8" t="inlineStr">
@@ -9572,7 +9556,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L117" s="10" t="inlineStr">
+      <c r="L117" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -9595,12 +9579,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Belumosudil Tablets 200 Mg</t>
+          <t>Bevacizumab</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -9615,22 +9599,22 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Belumosudil Mesylate 200.0000 Milligram (Mg)</t>
+          <t>Bevacizumab 100.0000 Mg/4ml (25 Mg/Ml)</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Concentrate solution for infusion</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Indicated For The Treatment Of Patients 12 Years And Older With Chronic Graftversus-Host Disease(Cgvhd) After Failure Of At Least Two Prior Lines Of Systemic Therapy.</t>
+          <t>Hepatocellular Carcinoma (Hcc)</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>MSN Laboratories Private Limited</t>
+          <t>Dr Reddys Laboratories Limited</t>
         </is>
       </c>
       <c r="I118" s="8" t="inlineStr">
@@ -9648,7 +9632,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L118" s="9" t="inlineStr">
+      <c r="L118" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -9671,12 +9655,12 @@
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Infliximab</t>
+          <t>Belumosudil Mesylate-Bulk Drug</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -9686,37 +9670,37 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>Infliximab 100.0000 Milligram (Mg),Sodium Phosphate, Monobasic, Monohydrate 2.2000 Milligram (Mg),Sucrose 500.0000 Milligram (Mg),Sodium Phosphate, Dibasic Dihydrate 6.1000 Milligram (Mg),Polysorbate 80 0.5000 Milligram (Mg)</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>The recommended dose of REZUROCK is 200 mg given orally once daily until progression of chronic GVHD that requires new systemic therapy.</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>Rheumatoid Arthritis,Adult Crohn?S Disease,Paediatric Crohn?S Disease,Ulcerative Colitis,Ankylosing Spondylitis,Psoriatic Arthritis,Psoriasis</t>
+          <t>REZUROCK is indicated for the treatment of adult and pediatric patients 12 years and older with chronic graft-versus-host disease (chronic GVHD) after failure of at least two prior lines of systemic therapy.</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>MSN Organics Private Limited</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
@@ -9724,19 +9708,27 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L119" s="10" t="inlineStr">
+      <c r="L119" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
+          <t>2026-07-08 17:33:33</t>
         </is>
       </c>
       <c r="N119" s="6" t="inlineStr"/>
-      <c r="O119" s="6" t="inlineStr"/>
-      <c r="P119" s="6" t="inlineStr"/>
+      <c r="O119" s="6" t="inlineStr">
+        <is>
+          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2021/214783s000lbl.pdf</t>
+        </is>
+      </c>
+      <c r="P119" s="6" t="inlineStr">
+        <is>
+          <t>https://www.accessdata.fda.gov/drugsatfda_docs/label/2021/214783s000lbl.pdf</t>
+        </is>
+      </c>
       <c r="Q119" s="6" t="b">
         <v>0</v>
       </c>
@@ -9747,12 +9739,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Velaglucerase Alfa</t>
+          <t>Belumosudil Tablets 200 Mg</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -9767,22 +9759,22 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Velaglucerase Alfa 10.0000 Milligram (Mg),Sucrose 200.0000 Milligram (Mg),Sodium Citrate, Dehydrate 51.7600 Milligram (Mg),Citric Acid, Monohydrate 5.0400 Milligram (Mg),Polysorbate 20 0.4400 Milligram (Mg)</t>
+          <t>Belumosudil Mesylate 200.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Powder for Solution for Infusion in SDV</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>Velaglucerase Alfa Is Indicated For Long-Term Enzyme Replacement Therapy (Ert) In Patients With Type 1, And Chronic Neuronopathic (Type 3) Gaucher Disease Who Exhibit Clinically Significant Non-Neurological Manifestations Of The Disease</t>
+          <t>Indicated For The Treatment Of Patients 12 Years And Older With Chronic Graftversus-Host Disease(Cgvhd) After Failure Of At Least Two Prior Lines Of Systemic Therapy.</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
+          <t>MSN Laboratories Private Limited</t>
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr">
@@ -9800,7 +9792,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L120" s="9" t="inlineStr">
+      <c r="L120" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -9823,12 +9815,12 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Avibactam 500 Mg+Aztreonam 1500 Mg</t>
+          <t>Infliximab</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -9843,7 +9835,7 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>Aztreonam 1500.0000 Milligram (Mg),Avibactam Sodium Equivalent To Avibactam 500.0000 Milligram (Mg)</t>
+          <t>Infliximab 100.0000 Milligram (Mg),Sodium Phosphate, Monobasic, Monohydrate 2.2000 Milligram (Mg),Sucrose 500.0000 Milligram (Mg),Sodium Phosphate, Dibasic Dihydrate 6.1000 Milligram (Mg),Polysorbate 80 0.5000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
@@ -9853,12 +9845,12 @@
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>For The Treatment Of The Following Infections In Adult Patients- Complicated Intra Abdominal Infection, Hospital Acquired Pneumonia, Including Ventilator Associated Pneumonia, Complicated Urinary Tract Infection, Including Pyelonephritis. It Is Also Indicated For The Treatment Of Infections Due To Aerobic Gram Negative Organisms In Adult Patients With Limited Treatment Options. Consideration Should Be Given To Official Guidance On The Appropriate Use Of Antibacterial Agents.</t>
+          <t>Rheumatoid Arthritis,Adult Crohn?S Disease,Paediatric Crohn?S Disease,Ulcerative Colitis,Ankylosing Spondylitis,Psoriatic Arthritis,Psoriasis</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>BDR Pharmaceuticals International Pvt Ltd</t>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I121" s="8" t="inlineStr">
@@ -9876,7 +9868,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L121" s="10" t="inlineStr">
+      <c r="L121" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -9904,7 +9896,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Trastuzumab Deruxtecan Powder For Concentrate For Solution For Infusion</t>
+          <t>Velaglucerase Alfa</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -9919,22 +9911,22 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Trastuzumab Deruxtecan 100.0000 Mg/5ml,Sucrose 450.0000 Milligram (Mg),L-Histidine 4.4500 Milligram (Mg),L-Histidine Hydrochloride Monohydrate 20.2000 Milligram (Mg),Polysorbate 80 1.5000 Milligram (Mg)</t>
+          <t>Velaglucerase Alfa 10.0000 Milligram (Mg),Sucrose 200.0000 Milligram (Mg),Sodium Citrate, Dehydrate 51.7600 Milligram (Mg),Citric Acid, Monohydrate 5.0400 Milligram (Mg),Polysorbate 20 0.4400 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Powder for concentrate for solution for infusion</t>
+          <t>Powder for Solution for Infusion in SDV</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Enhertu In Combination With Pertuzumab Is Indicated For The First-Line Treatment Of Adult Patients With Unresectable Or Metastatic Her2-Positive (Ihc3+ Or Ish+) Breast Cancer.</t>
+          <t>Velaglucerase Alfa Is Indicated For Long-Term Enzyme Replacement Therapy (Ert) In Patients With Type 1, And Chronic Neuronopathic (Type 3) Gaucher Disease Who Exhibit Clinically Significant Non-Neurological Manifestations Of The Disease</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>AstraZeneca Pharma India Limited</t>
+          <t>Takeda Biopharmaceuticals India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
@@ -9952,7 +9944,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L122" s="9" t="inlineStr">
+      <c r="L122" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -9975,12 +9967,12 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Inactivated Poliomyelitis Vaccine I.P.</t>
+          <t>Avibactam 500 Mg+Aztreonam 1500 Mg</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -9995,22 +9987,22 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 1 (Mahoney) 29.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 2 (Mef) 7.0000 D Antigen Units,Concentrated Trivalent Of Inactivated Poliomyelitis Virus- Type 3 (Saukett) 26.0000 D Antigen Units,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Phenoxyethanol 2.5000 ?l,2-Phenoxyethanol - Ethanol (50 % V/V Solution)- Ethanol 2.5000 ?l,Formaldehyde Solution 12.5000 ?l,Medium 199 Hanks 10xc Without Phenol Red 0.0000 Q.S. To 0.5 Ml</t>
+          <t>Aztreonam 1500.0000 Milligram (Mg),Avibactam Sodium Equivalent To Avibactam 500.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>Suspension for injection</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>Active Immunization Of Infants, Children And Adults For Prevention Of Poliomyelitis</t>
+          <t>For The Treatment Of The Following Infections In Adult Patients- Complicated Intra Abdominal Infection, Hospital Acquired Pneumonia, Including Ventilator Associated Pneumonia, Complicated Urinary Tract Infection, Including Pyelonephritis. It Is Also Indicated For The Treatment Of Infections Due To Aerobic Gram Negative Organisms In Adult Patients With Limited Treatment Options. Consideration Should Be Given To Official Guidance On The Appropriate Use Of Antibacterial Agents.</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+          <t>BDR Pharmaceuticals International Pvt Ltd</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -10028,7 +10020,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L123" s="10" t="inlineStr">
+      <c r="L123" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -10051,12 +10043,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin+Metoprolol Sr</t>
+          <t>Trastuzumab Deruxtecan Powder For Concentrate For Solution For Infusion</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -10071,22 +10063,22 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Metoprolol Succinate 25.0000 Milligram (Mg)</t>
+          <t>Trastuzumab Deruxtecan 100.0000 Mg/5ml,Sucrose 450.0000 Milligram (Mg),L-Histidine 4.4500 Milligram (Mg),L-Histidine Hydrochloride Monohydrate 20.2000 Milligram (Mg),Polysorbate 80 1.5000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Powder for concentrate for solution for infusion</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Heart Failure Post-Acute Myocardial Infarction</t>
+          <t>Enhertu In Combination With Pertuzumab Is Indicated For The First-Line Treatment Of Adult Patients With Unresectable Or Metastatic Her2-Positive (Ihc3+ Or Ish+) Breast Cancer.</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Limited</t>
+          <t>AstraZeneca Pharma India Limited</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -10104,7 +10096,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L124" s="9" t="inlineStr">
+      <c r="L124" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -10816,7 +10808,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Hepatitis A (Live) Vaccine, Freeze-Dried Injection</t>
+          <t>Tetanus Vaccine (Adsorbed) I.P.-Ready To Fill Bulk (Rtfb)</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -10826,37 +10818,37 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>Live Attenuated Hepatitis A Virus 6.5000 Log Ccid50</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>Vaccines (Lyophilized)</t>
+          <t>Bulk Drug</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>For Active Immunization Against Infection Caused By Hepatitis A Virus</t>
+          <t>Adsorbed Tetanus Vaccine is indicated for active immunization against tetanus in adults, children and in infants 6 weeks of age or</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>Joint Force Pharamchem Pvt. Ltd.,</t>
-        </is>
-      </c>
-      <c r="I134" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>INDIAN IMMUNOLOGICAL LIMITED</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>composition, dosage</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
@@ -10864,19 +10856,31 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L134" s="9" t="inlineStr">
+      <c r="L134" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N134" s="3" t="inlineStr"/>
-      <c r="O134" s="3" t="inlineStr"/>
-      <c r="P134" s="3" t="inlineStr"/>
+          <t>2026-07-08 17:33:08</t>
+        </is>
+      </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/01.SmPC%20-%20Tetanus%20Vaccine%20(Bio%20E.%20Ltd).pdf</t>
+        </is>
+      </c>
       <c r="Q134" s="3" t="b">
         <v>0</v>
       </c>
@@ -10892,7 +10896,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Tetanus Vaccine (Adsorbed) I.P.-Ready To Fill Bulk (Rtfb)</t>
+          <t>Hepatitis A (Live) Vaccine, Freeze-Dried Injection</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -10902,37 +10906,37 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
+          <t>Finished Formulation</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>Live Attenuated Hepatitis A Virus 6.5000 Log Ccid50</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>Vaccines (Lyophilized)</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>Adsorbed Tetanus Vaccine is indicated for active immunization against tetanus in adults, children and in infants 6 weeks of age or</t>
+          <t>For Active Immunization Against Infection Caused By Hepatitis A Virus</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>INDIAN IMMUNOLOGICAL LIMITED</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Joint Force Pharamchem Pvt. Ltd.,</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>composition, dosage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -10940,31 +10944,19 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L135" s="10" t="inlineStr">
+      <c r="L135" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:33:08</t>
-        </is>
-      </c>
-      <c r="N135" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="O135" s="4" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="P135" s="10" t="inlineStr">
-        <is>
-          <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/01.SmPC%20-%20Tetanus%20Vaccine%20(Bio%20E.%20Ltd).pdf</t>
-        </is>
-      </c>
+          <t>01-Jul-2026 00:52</t>
+        </is>
+      </c>
+      <c r="N135" s="6" t="inlineStr"/>
+      <c r="O135" s="6" t="inlineStr"/>
+      <c r="P135" s="6" t="inlineStr"/>
       <c r="Q135" s="6" t="b">
         <v>0</v>
       </c>
@@ -10980,7 +10972,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Mavacamten capsules 2.5mg,5 mg,10mg,15 mg</t>
+          <t>Ferumoxytol Bulk Drug &amp;Ferumoxytol Injection 510 mg Elemental Iron/17mL(30mg/mL)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -10990,7 +10982,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Capsule</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -11005,7 +10997,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Mavacmten is indicated for the treatment of symptomatic (NEW York Heart Association, NYHA, class II-III) obstructive hypertrophic cardiomyopathy(oHCM) in adult patients.</t>
+          <t>It is an iron replacement product indicated for the treatment of iron deficiency anemia(IDA) in adult patients:  who have intolerance to oral iron or have had unsatisfactory response to oral iron or  who have chronic kidney disease(CKD)</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -11045,7 +11037,7 @@
         <v>1</v>
       </c>
       <c r="R136" s="5" t="n">
-        <v>46211.741485</v>
+        <v>46211.74148579861</v>
       </c>
     </row>
     <row r="137">
@@ -11056,7 +11048,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Ferumoxytol Bulk Drug &amp;Ferumoxytol Injection 510 mg Elemental Iron/17mL(30mg/mL)</t>
+          <t>Mavacamten capsules 2.5mg,5 mg,10mg,15 mg</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -11066,7 +11058,7 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Capsule</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -11081,7 +11073,7 @@
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>It is an iron replacement product indicated for the treatment of iron deficiency anemia(IDA) in adult patients:  who have intolerance to oral iron or have had unsatisfactory response to oral iron or  who have chronic kidney disease(CKD)</t>
+          <t>Mavacmten is indicated for the treatment of symptomatic (NEW York Heart Association, NYHA, class II-III) obstructive hypertrophic cardiomyopathy(oHCM) in adult patients.</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11121,7 +11113,7 @@
         <v>1</v>
       </c>
       <c r="R137" s="7" t="n">
-        <v>46211.74148579861</v>
+        <v>46211.741485</v>
       </c>
     </row>
     <row r="138">
@@ -11360,7 +11352,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Guselkumab</t>
+          <t>Diphtheria, Tetanus, Pertussis (Whole Cell), Hepatitis B (R-Dna), Inactivated Poliomyelitis And Haemophilus Influenzae Type B Conjugate Vaccine (Adsorbed) - Single Dose (0.5 Ml) And Multi Dose (2.5 Ml)</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -11370,27 +11362,27 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Both BD &amp; FF</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>Guselkumab 100.0000 Milligram (Mg),Sucrose 79.0000 Milligram (Mg),L-Histidine 0.6000 Milligram (Mg),L-Histidine Monohydrochloride Monohydrate 1.5000 Milligram (Mg),Polysorbate 80 0.5000 Milligram (Mg),Water For Injection 1.0000 Ml</t>
+          <t>B. Pertussis (Whole Cell, Killed) 4.0000 Iu,Inactivated Poliomyelitis Virus Type -2 (S19/Mef2p1/N18s) 8.0000 D Antigen Units,Inactivated Poliomyelitis Virus Type -1 (S19/Mahp1/N18s) 40.0000 D Antigen Units,Diphtheria Toxoid 30.0000 Iu,R-Hbsag (Recombinant Hbs Antigen Produced In Pichia Pastoris) 12.5000 Milligram (Mg),Tetanus Toxoid 60.0000 Iu,Purified Capsular Polysaccharide Of Hib (Prp) Covalently Linked To 20 To 36.7 ?g Of Tetanus Toxoid 11.0000 Micrograms (?g),Inactivated Poliomyelitis Virus Type -3 (S19/Sktp1/N18s) 32.0000 D Antigen Units,2-Phenoxyethanol 4.0000 Milligram (Mg),Al+++ (As Alpo4) 1.2500 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Vaccines (Liquid)</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>Guselkumab By Subcutaneous (Sc) Administration Is Indicated For: ? Treatment Of Plaque Psoriasis  ? Treatment Of Scalp Psoriasis, Nail Psoriasis, And Hand And Foot Psoriasis ? Improvement Of Health Related Quality Of Life In Adult Patients With Moderate To Severe Psoriasis Who Are Candidates For Phototherapy Or Systemic Therapy.</t>
+          <t>For Active Immunization To Prevent Diphtheria, Tetanus, Pertussis, Hepatitis B, Poliomyelitis Types 1, 2, 3 And Haemophilus Influenzae Type B</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
+          <t>Biological E - Shameerpet</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
@@ -11408,7 +11400,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L141" s="10" t="inlineStr">
+      <c r="L141" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11484,7 +11476,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L142" s="9" t="inlineStr">
+      <c r="L142" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11512,7 +11504,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Diphtheria, Tetanus, Pertussis (Whole Cell), Hepatitis B (R-Dna), Inactivated Poliomyelitis And Haemophilus Influenzae Type B Conjugate Vaccine (Adsorbed) - Single Dose (0.5 Ml) And Multi Dose (2.5 Ml)</t>
+          <t>Guselkumab</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -11522,27 +11514,27 @@
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Both BD &amp; FF</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>B. Pertussis (Whole Cell, Killed) 4.0000 Iu,Inactivated Poliomyelitis Virus Type -2 (S19/Mef2p1/N18s) 8.0000 D Antigen Units,Inactivated Poliomyelitis Virus Type -1 (S19/Mahp1/N18s) 40.0000 D Antigen Units,Diphtheria Toxoid 30.0000 Iu,R-Hbsag (Recombinant Hbs Antigen Produced In Pichia Pastoris) 12.5000 Milligram (Mg),Tetanus Toxoid 60.0000 Iu,Purified Capsular Polysaccharide Of Hib (Prp) Covalently Linked To 20 To 36.7 ?g Of Tetanus Toxoid 11.0000 Micrograms (?g),Inactivated Poliomyelitis Virus Type -3 (S19/Sktp1/N18s) 32.0000 D Antigen Units,2-Phenoxyethanol 4.0000 Milligram (Mg),Al+++ (As Alpo4) 1.2500 Milligram (Mg)</t>
+          <t>Guselkumab 100.0000 Milligram (Mg),Sucrose 79.0000 Milligram (Mg),L-Histidine 0.6000 Milligram (Mg),L-Histidine Monohydrochloride Monohydrate 1.5000 Milligram (Mg),Polysorbate 80 0.5000 Milligram (Mg),Water For Injection 1.0000 Ml</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>Vaccines (Liquid)</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>For Active Immunization To Prevent Diphtheria, Tetanus, Pertussis, Hepatitis B, Poliomyelitis Types 1, 2, 3 And Haemophilus Influenzae Type B</t>
+          <t>Guselkumab By Subcutaneous (Sc) Administration Is Indicated For: ? Treatment Of Plaque Psoriasis  ? Treatment Of Scalp Psoriasis, Nail Psoriasis, And Hand And Foot Psoriasis ? Improvement Of Health Related Quality Of Life In Adult Patients With Moderate To Severe Psoriasis Who Are Candidates For Phototherapy Or Systemic Therapy.</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>Biological E - Shameerpet</t>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
@@ -11560,7 +11552,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L143" s="10" t="inlineStr">
+      <c r="L143" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11632,7 +11624,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L144" s="9" t="inlineStr">
+      <c r="L144" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11642,17 +11634,17 @@
           <t>2026-07-08 17:31:42</t>
         </is>
       </c>
-      <c r="N144" s="9" t="inlineStr">
+      <c r="N144" s="3" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadCommitteeFiles/Recommendations%20Endocrinology%20%20Metabolism%2013.01.2025.pdf</t>
         </is>
       </c>
-      <c r="O144" s="9" t="inlineStr">
+      <c r="O144" s="3" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadCommitteeFiles/Recommendations%20Endocrinology%20%20Metabolism%2013.01.2025.pdf</t>
         </is>
       </c>
-      <c r="P144" s="9" t="inlineStr">
+      <c r="P144" s="3" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadCommitteeFiles/Recommendations%20Endocrinology%20%20Metabolism%2013.01.2025.pdf</t>
         </is>
@@ -11667,12 +11659,12 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Ranibizumab</t>
+          <t>Dapagliflozin Propanediol+Metformin Hydrochloride+Sitagliptin Phosphate Monohydrate</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -11687,22 +11679,22 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>Ranibizumab 10.0000 Mg/Ml,L Histidine 0.3210 Mg/Ml,L Histidine Hydrochloride Monohydrate 1.6620 Mg/Ml,?,? Trehalose Dihydrate 100.0000 Mg/Ml,Polysorbate 20 0.1000 Mg/Ml,Water For Injection 1.0000 Q.S To 1 Ml</t>
+          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Sitagliptin Phosphate Monohydrate 100.0000 Milligram (Mg),Metformin Hydrochloride 1000.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>The Treatment Of Neovascular (Wet) Age-Related Macular Degeneration (Amd),The Treatment Of Visual Impairment Due To Diabetic Macular Oedema (Dme),The Treatment Of Visual Impairment Due To Macular Oedema Secondary To Retinal Vein Occlusion (Branch Rvo Or Central Rvo),The Treatment Of Visual Impairment Due To Choroidal Neovascularisation (Cnv)</t>
+          <t>It Is Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus.</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>LUPIN LIMITED</t>
+          <t>Eris Therapeutics Limited</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
@@ -11720,7 +11712,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L145" s="10" t="inlineStr">
+      <c r="L145" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11737,7 +11729,7 @@
         <v>1</v>
       </c>
       <c r="R145" s="7" t="n">
-        <v>46211.72997633102</v>
+        <v>46211.72998680556</v>
       </c>
     </row>
     <row r="146">
@@ -11748,7 +11740,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol+Metformin Hydrochloride+Sitagliptin Phosphate Monohydrate</t>
+          <t>Fluticasone Furoate+Umeclidinium+Vilanterol</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -11763,22 +11755,22 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Sitagliptin Phosphate Monohydrate 100.0000 Milligram (Mg),Metformin Hydrochloride 1000.0000 Milligram (Mg)</t>
+          <t>Fluticasone Furoate 200.0000 Micrograms (?g),Umeclidinium 62.5000 Micrograms (?g),Vilanterol 25.0000 Micrograms (?g)</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Dry Powder for Inhalation (in capsule)</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To Diet And Exercise To Improve Glycemic Control In Adults With Type 2 Diabetes Mellitus.</t>
+          <t>Indicated For The Maintenance Treatment Of Asthma In Patients Aged 18 Years And Older.</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>Eris Therapeutics Limited</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="I146" s="8" t="inlineStr">
@@ -11796,7 +11788,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L146" s="9" t="inlineStr">
+      <c r="L146" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11813,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="R146" s="5" t="n">
-        <v>46211.72998680556</v>
+        <v>46211.72998452546</v>
       </c>
     </row>
     <row r="147">
@@ -11824,7 +11816,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Fluticasone Furoate+Umeclidinium+Vilanterol</t>
+          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin 10 Mg+Vildagliptin Ip (As Sustained Release) 100mg</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -11839,22 +11831,22 @@
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>Fluticasone Furoate 200.0000 Micrograms (?g),Umeclidinium 62.5000 Micrograms (?g),Vilanterol 25.0000 Micrograms (?g)</t>
+          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin 10.0000 Milligram (Mg),Vildagliptin Ip (As Sustained Release) 100.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Dry Powder for Inhalation (in capsule)</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>Indicated For The Maintenance Treatment Of Asthma In Patients Aged 18 Years And Older.</t>
+          <t>It Is Indicated In Patients With Type 2 Diabetes Mallitus Inadequately Controlled On Metformin Monotherapy</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>Unison Pharmaceuticals Pvt Ltd</t>
         </is>
       </c>
       <c r="I147" s="8" t="inlineStr">
@@ -11872,7 +11864,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L147" s="10" t="inlineStr">
+      <c r="L147" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11889,18 +11881,18 @@
         <v>1</v>
       </c>
       <c r="R147" s="7" t="n">
-        <v>46211.72998452546</v>
+        <v>46211.72998199074</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin 10 Mg+Vildagliptin Ip (As Sustained Release) 100mg</t>
+          <t>Pertuzumab Injection (Rdna Origin) 420 Mg/14ml (Single Dose Vial With A Concentration Of 30mg/Ml)</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -11915,22 +11907,22 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol Usp Eq. To Dapagliflozin 10.0000 Milligram (Mg),Vildagliptin Ip (As Sustained Release) 100.0000 Milligram (Mg)</t>
+          <t>Pertuzumab Drug Substance (Rdna Origin) 30.0000 Mg/Ml,Succinic Acid 1.1800 Mg/Ml,Sucrose 41.1000 Mg/Ml,Polysorbate 20 0.2000 Mg/Ml,Sodium Hydroxide 6.0000 Q.S. To Ph 6.0,Water For Injection 1.0000 Q.S To 1.0 Ml</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Solution for infusion</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>It Is Indicated In Patients With Type 2 Diabetes Mallitus Inadequately Controlled On Metformin Monotherapy</t>
+          <t>For Use In Combination With Trastuzumab And Chemotherapy In The Neoadjuvant Treatment Of Adult Patients With Her2-Positive, Locally Advanced, Inflammatory, Or Early Stage Breast Cancer At High Risk Of Recurrence,For Use In Combination With Trastuzumab And Chemotherapy In The Adjuvant Treatment Of Adult Patients With Her2-Positive Early Breast Cancer At High Risk Of Recurrence</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>Unison Pharmaceuticals Pvt Ltd</t>
+          <t>Enzene Biosciences Ltd., Pune</t>
         </is>
       </c>
       <c r="I148" s="8" t="inlineStr">
@@ -11948,7 +11940,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L148" s="9" t="inlineStr">
+      <c r="L148" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -11965,7 +11957,7 @@
         <v>1</v>
       </c>
       <c r="R148" s="5" t="n">
-        <v>46211.72998199074</v>
+        <v>46211.72997946759</v>
       </c>
     </row>
     <row r="149">
@@ -11976,7 +11968,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Pertuzumab Injection (Rdna Origin) 420 Mg/14ml (Single Dose Vial With A Concentration Of 30mg/Ml)</t>
+          <t>Ranibizumab</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -11991,22 +11983,22 @@
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>Pertuzumab Drug Substance (Rdna Origin) 30.0000 Mg/Ml,Succinic Acid 1.1800 Mg/Ml,Sucrose 41.1000 Mg/Ml,Polysorbate 20 0.2000 Mg/Ml,Sodium Hydroxide 6.0000 Q.S. To Ph 6.0,Water For Injection 1.0000 Q.S To 1.0 Ml</t>
+          <t>Ranibizumab 10.0000 Mg/Ml,L Histidine 0.3210 Mg/Ml,L Histidine Hydrochloride Monohydrate 1.6620 Mg/Ml,?,? Trehalose Dihydrate 100.0000 Mg/Ml,Polysorbate 20 0.1000 Mg/Ml,Water For Injection 1.0000 Q.S To 1 Ml</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>Solution for infusion</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>For Use In Combination With Trastuzumab And Chemotherapy In The Neoadjuvant Treatment Of Adult Patients With Her2-Positive, Locally Advanced, Inflammatory, Or Early Stage Breast Cancer At High Risk Of Recurrence,For Use In Combination With Trastuzumab And Chemotherapy In The Adjuvant Treatment Of Adult Patients With Her2-Positive Early Breast Cancer At High Risk Of Recurrence</t>
+          <t>The Treatment Of Neovascular (Wet) Age-Related Macular Degeneration (Amd),The Treatment Of Visual Impairment Due To Diabetic Macular Oedema (Dme),The Treatment Of Visual Impairment Due To Macular Oedema Secondary To Retinal Vein Occlusion (Branch Rvo Or Central Rvo),The Treatment Of Visual Impairment Due To Choroidal Neovascularisation (Cnv)</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>Enzene Biosciences Ltd., Pune</t>
+          <t>LUPIN LIMITED</t>
         </is>
       </c>
       <c r="I149" s="8" t="inlineStr">
@@ -12024,7 +12016,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L149" s="10" t="inlineStr">
+      <c r="L149" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12041,7 +12033,7 @@
         <v>1</v>
       </c>
       <c r="R149" s="7" t="n">
-        <v>46211.72997946759</v>
+        <v>46211.72997633102</v>
       </c>
     </row>
     <row r="150">
@@ -12176,7 +12168,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L151" s="10" t="inlineStr">
+      <c r="L151" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12199,12 +12191,12 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Semaglutide Injection</t>
+          <t>Umeclidinium+Vilanterol</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -12219,22 +12211,22 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Semaglutide 1.0000 Mg/1.5 Ml</t>
+          <t>Vilanterol 25.0000 Micrograms (?g),Umeclidinium 62.5000 Micrograms (?g)</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Inhalation Powder</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of 30 Kg/M2 Or Greater (Obesity). Or 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia).</t>
+          <t>For The Maintenance Treatment Of Patients With Chronic Obstructive Pulmonary Disease (Copd).</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>Natco Pharma Limited</t>
+          <t>Zydus Healthcare Limited</t>
         </is>
       </c>
       <c r="I152" s="8" t="inlineStr">
@@ -12252,7 +12244,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L152" s="9" t="inlineStr">
+      <c r="L152" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12275,12 +12267,12 @@
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Ruxolitinib Phosphate</t>
+          <t>Bilastine 3.3 Mg+Dextromethorphan Hydrobromide 10 Mg+Phenylephrine Hydrochloride 5 Mg Syrup</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -12290,27 +12282,27 @@
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>Ruxolitinib phosphate tablets</t>
+          <t>Dextromethorphan Hydrobromide 10.0000 Milligram (Mg),Bilastine 3.3000 Milligram (Mg),Phenylephrine Hydrochloride 5.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>Recommended Initial Ruxolitinib Dosage: &gt;=100,000/mm3: 10 mg twice daily; 50,000 to &lt;100,000/mm3: 5 mg twice daily. Other dosages include 5 mg, 10 mg, 15 mg, 20 mg, or 25 mg twice daily.</t>
+          <t>Syrup</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>Ruxolitinib Phosphate has been primarily indicated for the treatment of myelofibrosis, a rare type of bone marrow cancer, and polycythemia vera, a condition characterized by an overproduction of red blood cells.</t>
+          <t>For Relief Of Coughs And Upper Respiratory Symptoms, Including Nasal Congestion, Associated With Allergy Or The Common Cold</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>Natco Pharma Limited</t>
+          <t>Windlas Biotech Limited</t>
         </is>
       </c>
       <c r="I153" s="8" t="inlineStr">
@@ -12318,37 +12310,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J153" s="6" t="inlineStr"/>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L153" s="10" t="inlineStr">
+      <c r="L153" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-08 17:34:52</t>
-        </is>
-      </c>
-      <c r="N153" s="10" t="inlineStr">
-        <is>
-          <t>https://www.accessdata.fda.gov/drugsatfda_docs/nda/2011/202192Orig1s000ChemR.pdf</t>
-        </is>
-      </c>
-      <c r="O153" s="10" t="inlineStr">
-        <is>
-          <t>https://www.oncologynewscentral.com/drugs/monograph/158425-312013/ruxolitinib-oral</t>
-        </is>
-      </c>
-      <c r="P153" s="10" t="inlineStr">
-        <is>
-          <t>https://synapse.patsnap.com/article/what-is-ruxolitinib-phosphate-used-for</t>
-        </is>
-      </c>
+          <t>01-Jul-2026 00:52</t>
+        </is>
+      </c>
+      <c r="N153" s="6" t="inlineStr"/>
+      <c r="O153" s="6" t="inlineStr"/>
+      <c r="P153" s="6" t="inlineStr"/>
       <c r="Q153" s="6" t="b">
         <v>0</v>
       </c>
@@ -12359,12 +12343,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Tegoprazan Tablets 50 Mg And 25 Mg</t>
+          <t>Eplerenone+Torsemide</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -12379,22 +12363,22 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Tegoprazan 25.0000 Milligram (Mg)</t>
+          <t>Torsemide 10.0000 Milligram (Mg),Eplerenone 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>Uncoated Tablets</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Tegoprazan Tablet 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non Erosive Gastroesophageal Reflux Disease And Gastric Ulcer,Tegoprazan Tablet 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease</t>
+          <t>Indicated In Patients With Congestive Heart Failure.</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>Dr. Reddys Laboratories Limited</t>
+          <t>Exemed Pharmaceuticals</t>
         </is>
       </c>
       <c r="I154" s="8" t="inlineStr">
@@ -12412,7 +12396,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L154" s="9" t="inlineStr">
+      <c r="L154" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12435,12 +12419,12 @@
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Eplerenone+Torsemide</t>
+          <t>Tegoprazan Tablets 50 Mg And 25 Mg</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -12455,22 +12439,22 @@
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>Torsemide 10.0000 Milligram (Mg),Eplerenone 25.0000 Milligram (Mg)</t>
+          <t>Tegoprazan 25.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>Uncoated Tablets</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>Indicated In Patients With Congestive Heart Failure.</t>
+          <t>Tegoprazan Tablet 50 Mg Is Indicated For Erosive Gastroesophageal Reflux Disease, Non Erosive Gastroesophageal Reflux Disease And Gastric Ulcer,Tegoprazan Tablet 25 Mg Is Indicated For Maintenance Of Healed Erosive Gastroesophageal Reflux Disease</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>Exemed Pharmaceuticals</t>
+          <t>Dr. Reddys Laboratories Limited</t>
         </is>
       </c>
       <c r="I155" s="8" t="inlineStr">
@@ -12488,7 +12472,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L155" s="10" t="inlineStr">
+      <c r="L155" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12511,12 +12495,12 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Bilastine 3.3 Mg+Dextromethorphan Hydrobromide 10 Mg+Phenylephrine Hydrochloride 5 Mg Syrup</t>
+          <t>Semaglutide Injection</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -12531,22 +12515,22 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Dextromethorphan Hydrobromide 10.0000 Milligram (Mg),Bilastine 3.3000 Milligram (Mg),Phenylephrine Hydrochloride 5.0000 Milligram (Mg)</t>
+          <t>Semaglutide 1.0000 Mg/1.5 Ml</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Syrup</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>For Relief Of Coughs And Upper Respiratory Symptoms, Including Nasal Congestion, Associated With Allergy Or The Common Cold</t>
+          <t>It Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adults With An Initial Body Mass Index (Bmi) Of 30 Kg/M2 Or Greater (Obesity). Or 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia).</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>Windlas Biotech Limited</t>
+          <t>Natco Pharma Limited</t>
         </is>
       </c>
       <c r="I156" s="8" t="inlineStr">
@@ -12564,7 +12548,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L156" s="9" t="inlineStr">
+      <c r="L156" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12587,12 +12571,12 @@
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Umeclidinium+Vilanterol</t>
+          <t>Ruxolitinib Phosphate</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -12602,27 +12586,27 @@
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>Vilanterol 25.0000 Micrograms (?g),Umeclidinium 62.5000 Micrograms (?g)</t>
+          <t>Ruxolitinib phosphate tablets</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>Inhalation Powder</t>
+          <t>Recommended Initial Ruxolitinib Dosage: &gt;=100,000/mm3: 10 mg twice daily; 50,000 to &lt;100,000/mm3: 5 mg twice daily. Other dosages include 5 mg, 10 mg, 15 mg, 20 mg, or 25 mg twice daily.</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>For The Maintenance Treatment Of Patients With Chronic Obstructive Pulmonary Disease (Copd).</t>
+          <t>Ruxolitinib Phosphate has been primarily indicated for the treatment of myelofibrosis, a rare type of bone marrow cancer, and polycythemia vera, a condition characterized by an overproduction of red blood cells.</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>Zydus Healthcare Limited</t>
+          <t>Natco Pharma Limited</t>
         </is>
       </c>
       <c r="I157" s="8" t="inlineStr">
@@ -12630,29 +12614,37 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J157" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J157" s="6" t="inlineStr"/>
       <c r="K157" s="6" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L157" s="10" t="inlineStr">
+      <c r="L157" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
-          <t>01-Jul-2026 00:52</t>
-        </is>
-      </c>
-      <c r="N157" s="6" t="inlineStr"/>
-      <c r="O157" s="6" t="inlineStr"/>
-      <c r="P157" s="6" t="inlineStr"/>
+          <t>2026-07-08 17:34:52</t>
+        </is>
+      </c>
+      <c r="N157" s="6" t="inlineStr">
+        <is>
+          <t>https://www.accessdata.fda.gov/drugsatfda_docs/nda/2011/202192Orig1s000ChemR.pdf</t>
+        </is>
+      </c>
+      <c r="O157" s="6" t="inlineStr">
+        <is>
+          <t>https://www.oncologynewscentral.com/drugs/monograph/158425-312013/ruxolitinib-oral</t>
+        </is>
+      </c>
+      <c r="P157" s="6" t="inlineStr">
+        <is>
+          <t>https://synapse.patsnap.com/article/what-is-ruxolitinib-phosphate-used-for</t>
+        </is>
+      </c>
       <c r="Q157" s="6" t="b">
         <v>0</v>
       </c>
@@ -12668,7 +12660,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Bisoprolol Fumarate+Cilnidipine</t>
+          <t>Dapagliflozin Propanediol+Pioglitazone Hydrochloride</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -12683,7 +12675,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Bisoprolol Fumarate 2.5000 Milligram (Mg)</t>
+          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Pioglitazone Hydrochloride 15.0000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -12693,12 +12685,12 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>Treatment Of Essential Hypertension</t>
+          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>Unique Pharmaceutical Laboratories (A Division Of J. B. Chemicals &amp; Pharmaceuticals Limited)</t>
+          <t>Eris Therapeutics Limited</t>
         </is>
       </c>
       <c r="I158" s="8" t="inlineStr">
@@ -12716,7 +12708,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L158" s="9" t="inlineStr">
+      <c r="L158" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12733,7 +12725,7 @@
         <v>1</v>
       </c>
       <c r="R158" s="5" t="n">
-        <v>46211.72999200231</v>
+        <v>46211.72999569445</v>
       </c>
     </row>
     <row r="159">
@@ -12744,7 +12736,7 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol+Pioglitazone Hydrochloride</t>
+          <t>Bisoprolol Fumarate+Cilnidipine</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -12759,7 +12751,7 @@
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>Dapagliflozin Propanediol 10.0000 Milligram (Mg),Pioglitazone Hydrochloride 15.0000 Milligram (Mg)</t>
+          <t>Bisoprolol Fumarate 2.5000 Milligram (Mg)</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
@@ -12769,12 +12761,12 @@
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
+          <t>Treatment Of Essential Hypertension</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>Eris Therapeutics Limited</t>
+          <t>Unique Pharmaceutical Laboratories (A Division Of J. B. Chemicals &amp; Pharmaceuticals Limited)</t>
         </is>
       </c>
       <c r="I159" s="8" t="inlineStr">
@@ -12792,7 +12784,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L159" s="10" t="inlineStr">
+      <c r="L159" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -12809,7 +12801,7 @@
         <v>1</v>
       </c>
       <c r="R159" s="7" t="n">
-        <v>46211.72999569445</v>
+        <v>46211.72999200231</v>
       </c>
     </row>
     <row r="160">
@@ -13248,7 +13240,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L165" s="10" t="inlineStr">
+      <c r="L165" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -13324,7 +13316,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L166" s="9" t="inlineStr">
+      <c r="L166" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -13396,7 +13388,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L167" s="10" t="inlineStr">
+      <c r="L167" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -13406,17 +13398,17 @@
           <t>2026-07-08 17:31:57</t>
         </is>
       </c>
-      <c r="N167" s="10" t="inlineStr">
+      <c r="N167" s="6" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
       </c>
-      <c r="O167" s="10" t="inlineStr">
+      <c r="O167" s="6" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
       </c>
-      <c r="P167" s="10" t="inlineStr">
+      <c r="P167" s="6" t="inlineStr">
         <is>
           <t>https://cdsco.gov.in/opencms/resources/UploadCDSCOWeb/2018/UploadSmPC/Tdap%20vaccine%20%20of%20Serum.pdf</t>
         </is>
@@ -13556,7 +13548,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L169" s="10" t="inlineStr">
+      <c r="L169" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -13566,17 +13558,17 @@
           <t>2026-07-02 00:55:47</t>
         </is>
       </c>
-      <c r="N169" s="10" t="inlineStr">
+      <c r="N169" s="6" t="inlineStr">
         <is>
           <t>https://pdf.hres.ca/dpd_pm/00076541.PDF</t>
         </is>
       </c>
-      <c r="O169" s="10" t="inlineStr">
+      <c r="O169" s="6" t="inlineStr">
         <is>
           <t>https://www.rxlist.com/sugammadex_sodium/generic-drug.htm</t>
         </is>
       </c>
-      <c r="P169" s="10" t="inlineStr">
+      <c r="P169" s="6" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/health/documents/community-register/2023/20230526159142/anx_159142_en.pdf</t>
         </is>
@@ -13948,7 +13940,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L174" s="9" t="inlineStr">
+      <c r="L174" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -13959,12 +13951,12 @@
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr"/>
-      <c r="O174" s="9" t="inlineStr">
+      <c r="O174" s="3" t="inlineStr">
         <is>
           <t>https://www.mayoclinic.org/drugs-supplements/venetoclax-oral-route/description/drg-20311676</t>
         </is>
       </c>
-      <c r="P174" s="9" t="inlineStr">
+      <c r="P174" s="3" t="inlineStr">
         <is>
           <t>https://reference.medscape.com/drug/venclexta-venetoclax-1000078</t>
         </is>
@@ -14032,7 +14024,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L175" s="10" t="inlineStr">
+      <c r="L175" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -14412,7 +14404,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L180" s="9" t="inlineStr">
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -14500,7 +14492,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L181" s="10" t="inlineStr">
+      <c r="L181" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -14576,7 +14568,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L182" s="9" t="inlineStr">
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -14652,7 +14644,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L183" s="10" t="inlineStr">
+      <c r="L183" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -14675,12 +14667,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Lazertinib Film Coated Tablets 80mg And 240 Mg</t>
+          <t>Polmacoxib</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -14690,27 +14682,27 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Lazertinib Mesylate Monohydrate 96.4800 Milligram (Mg),Hydrophobic Colloidal Silica 1.9000 Milligram (Mg),Microcrystalline Cellulose 218.3200 Milligram (Mg),Mannitol 50.0000 Milligram (Mg),Croscarmellose Sodium 9.5000 Milligram (Mg),Magnesium Stearate 3.8000 Milligram (Mg),Opadry Qx 321a220024 Yellow 11.4000 Milligram (Mg),Purified Water 0.0000 Removed During Processing</t>
+          <t>Polmacoxib 2 Mg</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Tablets</t>
+          <t>The recommended dose for adults is one film-coated tablet (2mg) once a day, to be administered after a meal or as directed by a physician. Do not exceed the 2mg daily dose.</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>In Combination With Amivantamab Is Indicated For The First-Line Treatment Of Adult Patients With Locally Advanced Or Metastatic Non-Small Cell Lung Cancer (Nsclc) With Epidermal Growth Factor Receptor (Egfr) Exon 19 Deletions Or Exon 21 L858r Substitution Mutations.</t>
+          <t>Localized Primary Osteoarthritis of Knee, Localized Primary Osteoarthritis of Hip, Rheumatoid joint pain, Postoperative torment, Potential Cardiovascular Risk Reduction in OA patients</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
+          <t>RESPECT LABS LLP</t>
         </is>
       </c>
       <c r="I184" s="8" t="inlineStr">
@@ -14718,29 +14710,37 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J184" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J184" s="3" t="inlineStr"/>
       <c r="K184" s="3" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L184" s="9" t="inlineStr">
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>02-Jul-2026 00:50</t>
-        </is>
-      </c>
-      <c r="N184" s="3" t="inlineStr"/>
-      <c r="O184" s="3" t="inlineStr"/>
-      <c r="P184" s="3" t="inlineStr"/>
+          <t>2026-07-08 17:35:06</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.invisionmedi.com/polmaflex-2-polmacoxib-2-mg-capsules</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.invisionmedi.com/polmaflex-2-polmacoxib-2-mg-capsules</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.invisionmedi.com/polmaflex-2-polmacoxib-2-mg-capsules</t>
+        </is>
+      </c>
       <c r="Q184" s="3" t="b">
         <v>0</v>
       </c>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>Eluxadoline Tablets 75 Mg And 100 Mg</t>
+          <t>Lazertinib Film Coated Tablets 80mg And 240 Mg</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -14766,12 +14766,12 @@
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>Both BD &amp; FF</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Eluxadoline 90.0000 %</t>
+          <t>Lazertinib Mesylate Monohydrate 96.4800 Milligram (Mg),Hydrophobic Colloidal Silica 1.9000 Milligram (Mg),Microcrystalline Cellulose 218.3200 Milligram (Mg),Mannitol 50.0000 Milligram (Mg),Croscarmellose Sodium 9.5000 Milligram (Mg),Magnesium Stearate 3.8000 Milligram (Mg),Opadry Qx 321a220024 Yellow 11.4000 Milligram (Mg),Purified Water 0.0000 Removed During Processing</t>
         </is>
       </c>
       <c r="F185" s="6" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>Indicated In Adults For The Treatment Of Irritable Bowel Syndrome With Diarrhea (Ibs-D)</t>
+          <t>In Combination With Amivantamab Is Indicated For The First-Line Treatment Of Adult Patients With Locally Advanced Or Metastatic Non-Small Cell Lung Cancer (Nsclc) With Epidermal Growth Factor Receptor (Egfr) Exon 19 Deletions Or Exon 21 L858r Substitution Mutations.</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I185" s="8" t="inlineStr">
@@ -14804,7 +14804,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L185" s="10" t="inlineStr">
+      <c r="L185" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Polmacoxib</t>
+          <t>Semaglutide Injection (Synthetic Origin)</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -14842,27 +14842,27 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Finished Formulation</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Polmacoxib 2 Mg</t>
+          <t>Semaglutide 0.6800 Mg/Ml</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>The recommended dose for adults is one film-coated tablet (2mg) once a day, to be administered after a meal or as directed by a physician. Do not exceed the 2mg daily dose.</t>
+          <t>Solution for injection</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>Localized Primary Osteoarthritis of Knee, Localized Primary Osteoarthritis of Hip, Rheumatoid joint pain, Postoperative torment, Potential Cardiovascular Risk Reduction in OA patients</t>
+          <t>Semaglutide Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adult With An Initial Body Mass Index (Bmi) Of ? 30 Kg/M2 Or Greater (Obesity) Or ? 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia).</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>RESPECT LABS LLP</t>
+          <t>Emcure Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="I186" s="8" t="inlineStr">
@@ -14870,37 +14870,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L186" s="9" t="inlineStr">
+      <c r="L186" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08 17:35:06</t>
-        </is>
-      </c>
-      <c r="N186" s="9" t="inlineStr">
-        <is>
-          <t>https://www.invisionmedi.com/polmaflex-2-polmacoxib-2-mg-capsules</t>
-        </is>
-      </c>
-      <c r="O186" s="9" t="inlineStr">
-        <is>
-          <t>https://www.invisionmedi.com/polmaflex-2-polmacoxib-2-mg-capsules</t>
-        </is>
-      </c>
-      <c r="P186" s="9" t="inlineStr">
-        <is>
-          <t>https://www.invisionmedi.com/polmaflex-2-polmacoxib-2-mg-capsules</t>
-        </is>
-      </c>
+          <t>02-Jul-2026 00:50</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr"/>
+      <c r="O186" s="3" t="inlineStr"/>
+      <c r="P186" s="3" t="inlineStr"/>
       <c r="Q186" s="3" t="b">
         <v>0</v>
       </c>
@@ -14916,7 +14908,7 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>Semaglutide Injection (Synthetic Origin)</t>
+          <t>Semaglutide Injection 2mg/3ml, 4mg/3ml &amp; 8mg/3ml</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
@@ -14936,17 +14928,19 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>Solution for injection</t>
+          <t>Pre Filled Pen</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>Semaglutide Is Indicated As An Adjunct To A Reduced Calorie Diet And Increased Physical Activity For Chronic Weight Management In Adult With An Initial Body Mass Index (Bmi) Of ? 30 Kg/M2 Or Greater (Obesity) Or ? 27 Kg/M2 Or Greater (Overweight) In The Presence Of At Least One Weight-Related Comorbid Condition (E.G., Hypertension, Type 2 Diabetes Mellitus, Or Dyslipidemia).</t>
+          <t>Semaglutide Is Indicated For The Treatment Of Adults With Insufficiently Controlled Type 2 Diabetes Mellitus As An Adjunct To Diet And Exercise
+As Monotherapy, When Metformin-Based Therapy Is Considered Inappropriate Due To Intolerance Or Contraindications.
+In Addition To Other Medicinal Products For The Treatment Of Diabetes.</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Limited</t>
+          <t>Precise Biopharma Pvt. Ltd.</t>
         </is>
       </c>
       <c r="I187" s="8" t="inlineStr">
@@ -14964,7 +14958,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L187" s="10" t="inlineStr">
+      <c r="L187" s="6" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -14987,12 +14981,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Semaglutide Injection 2mg/3ml, 4mg/3ml &amp; 8mg/3ml</t>
+          <t>Eluxadoline Tablets 75 Mg And 100 Mg</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -15002,29 +14996,27 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Finished Formulation</t>
+          <t>Both BD &amp; FF</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Semaglutide 0.6800 Mg/Ml</t>
+          <t>Eluxadoline 90.0000 %</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Pre Filled Pen</t>
+          <t>Tablets</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>Semaglutide Is Indicated For The Treatment Of Adults With Insufficiently Controlled Type 2 Diabetes Mellitus As An Adjunct To Diet And Exercise
-As Monotherapy, When Metformin-Based Therapy Is Considered Inappropriate Due To Intolerance Or Contraindications.
-In Addition To Other Medicinal Products For The Treatment Of Diabetes.</t>
+          <t>Indicated In Adults For The Treatment Of Irritable Bowel Syndrome With Diarrhea (Ibs-D)</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>Precise Biopharma Pvt. Ltd.</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="I188" s="8" t="inlineStr">
@@ -15042,7 +15034,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L188" s="9" t="inlineStr">
+      <c r="L188" s="3" t="inlineStr">
         <is>
           <t>https://www.cdscoonline.gov.in/CDSCO/cdscoDrugs</t>
         </is>
@@ -15118,7 +15110,7 @@
           <t>CDSCO</t>
         </is>
       </c>
-      <c r="L189" s="10" t="inlineStr">
+      <c r="L189" s="6" t="inlineStr">
         <is>
           <t>https://www.cdsco.gov.in</t>
         </is>
@@ -15234,7 +15226,7 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>Niraparib Tablet 100mg</t>
+          <t>Polmacoxib Bulk Drug, Polmacoxib Capsule 2mg</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -15244,7 +15236,7 @@
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Bulk Drug</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -15259,7 +15251,7 @@
       </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>Niraparib is indicated as monotherapy for the maintenance treatment of adult patients with advanced epithelial (FIGO stage-III and IV) high- grade ovarian, fallopian tube or primary peritoneal cancer who are in response (complete or partial) following completion of first-line platinum -based chemotherapy. as monotherapy for the maintenance treatment of adult patients with platinum- sensitive relapsed high grade serous epithelial ovarian, fallopian tube , or primary peritoneal cancer who are in response (complete or partia) to platinum- based chemotherapy</t>
+          <t>Indicatged for treatment of Idiopathic (primary) osteoarthritis of Hip/Knec</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15299,7 +15291,7 @@
         <v>1</v>
       </c>
       <c r="R191" s="7" t="n">
-        <v>46211.74144534722</v>
+        <v>46211.74144603009</v>
       </c>
     </row>
     <row r="192">
@@ -15310,7 +15302,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Polmacoxib Bulk Drug, Polmacoxib Capsule 2mg</t>
+          <t>Niraparib Tablet 100mg</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -15320,7 +15312,7 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Bulk Drug</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -15335,7 +15327,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>Indicatged for treatment of Idiopathic (primary) osteoarthritis of Hip/Knec</t>
+          <t>Niraparib is indicated as monotherapy for the maintenance treatment of adult patients with advanced epithelial (FIGO stage-III and IV) high- grade ovarian, fallopian tube or primary peritoneal cancer who are in response (complete or partial) following completion of first-line platinum -based chemotherapy. as monotherapy for the maintenance treatment of adult patients with platinum- sensitive relapsed high grade serous epithelial ovarian, fallopian tube , or primary peritoneal cancer who are in response (complete or partia) to platinum- based chemotherapy</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15375,7 +15367,7 @@
         <v>1</v>
       </c>
       <c r="R192" s="5" t="n">
-        <v>46211.74144603009</v>
+        <v>46211.74144534722</v>
       </c>
     </row>
     <row r="193">
@@ -15456,182 +15448,745 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R193"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N105" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N110" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N153" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N167" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P167" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N169" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P169" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P174" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N186" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P186" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId174"/>
-  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>drug_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>approval_date</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>original_indication</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>specific_indication</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>icd_code</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>icd_indication</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>level_1_indication</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Dapagliflozin+Metformin Hydrochloride Sr+Pioglitazone</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Eris Lifesciences Limited</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>26-MAY-2026</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Indicated In Patients With Type 2 Diabetes Mellitus Inadequately Controlled On Earlier Metformin Containing Monotherapy</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>E11.2</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Type 2 diabetes mellitus with renal complications</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Endocrine, nutritional and metabolic diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Vericiguat tablets 2.5mg/ 5mg/ 10mg</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>25-02-2022</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Indicated to reduce the risk of cardiovascular death and heart failure (HF) hospitalization following a hospitalization for heart failure or need for outpatient IV diuretics, in adults with symptomatic chronic HF and ejection fraction less than 45%</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Indicated to reduce the risk of cardiovascular death and heart failure (HF) hospitalization</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>I13.0</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Hypertensive heart and renal disease with (congestive) heart failure</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Nirmatrelvir bulk and Combipack of Nirmatrelvir 300mg tablets (2x150mg tablets) and Ritonavir tablets 100mg</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>21-04-2022</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>For treatment of adult patients with COVID-19, with SpO2 &gt;93% and who have high risk of progression of the disease including hospitalization or death, in light of Covid 19 outbreak for restricted emergency use in the country</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>For treatment of adult patients with COVID-19, with SpO2 &gt;93% and who have high risk of progression of the disease including hospitalization or death, in light of Covid 19 outbreak for restricted emergency use in the country</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Emergency use of U07</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Codes for special purposes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Bevacizumab</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>CuraTeQ Biologics Private Limited</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>14-MAY-2026</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Treatment Of Adult Patients With Metastatic Carcinoma Of The Colon Or Rectum,Treatment Of Adult Patients With Unresectable Advanced, Metastatic Or Recurrent Non-Small Cell Lung Cancer,Treatment Of Adult Patients With Advanced And/Or Metastatic Renal Cell Cancer,Treatment Of Adult Patients With Advanced Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer,Treatment Of Adult Patients With Persistent, Recurrent, Or Metastatic Carcinoma Of The Cervix</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Adult Patients With Advanced And/Or Metastatic Renal Cell Cancer</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>C64</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Malignant neoplasm of kidney, except renal pelvis</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Bevacizumab</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CuraTeQ Biologics Private Limited</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>14-MAY-2026</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Treatment Of Adult Patients With Metastatic Carcinoma Of The Colon Or Rectum,Treatment Of Adult Patients With Unresectable Advanced, Metastatic Or Recurrent Non-Small Cell Lung Cancer,Treatment Of Adult Patients With Advanced And/Or Metastatic Renal Cell Cancer,Treatment Of Adult Patients With Advanced Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer,Treatment Of Adult Patients With Persistent, Recurrent, Or Metastatic Carcinoma Of The Cervix</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Adult Patients With Advanced Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>C56</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Malignant neoplasm of ovary</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Bevacizumab</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>CuraTeQ Biologics Private Limited</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>14-MAY-2026</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Treatment Of Adult Patients With Metastatic Carcinoma Of The Colon Or Rectum,Treatment Of Adult Patients With Unresectable Advanced, Metastatic Or Recurrent Non-Small Cell Lung Cancer,Treatment Of Adult Patients With Advanced And/Or Metastatic Renal Cell Cancer,Treatment Of Adult Patients With Advanced Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer,Treatment Of Adult Patients With Persistent, Recurrent, Or Metastatic Carcinoma Of The Cervix</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Adult Patients With Metastatic Carcinoma Of The Colon Or Rectum</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>D37.4</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Neoplasm of uncertain or unknown behaviour: Colon</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Bevacizumab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>CuraTeQ Biologics Private Limited</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>14-MAY-2026</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Treatment Of Adult Patients With Metastatic Carcinoma Of The Colon Or Rectum,Treatment Of Adult Patients With Unresectable Advanced, Metastatic Or Recurrent Non-Small Cell Lung Cancer,Treatment Of Adult Patients With Advanced And/Or Metastatic Renal Cell Cancer,Treatment Of Adult Patients With Advanced Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer,Treatment Of Adult Patients With Persistent, Recurrent, Or Metastatic Carcinoma Of The Cervix</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Adult Patients With Persistent, Recurrent, Or Metastatic Carcinoma Of The Cervix</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Carcinoma in situ of cervix uteri</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Bevacizumab</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>CuraTeQ Biologics Private Limited</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>14-MAY-2026</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Treatment Of Adult Patients With Metastatic Carcinoma Of The Colon Or Rectum,Treatment Of Adult Patients With Unresectable Advanced, Metastatic Or Recurrent Non-Small Cell Lung Cancer,Treatment Of Adult Patients With Advanced And/Or Metastatic Renal Cell Cancer,Treatment Of Adult Patients With Advanced Epithelial Ovarian, Fallopian Tube, Or Primary Peritoneal Cancer,Treatment Of Adult Patients With Persistent, Recurrent, Or Metastatic Carcinoma Of The Cervix</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Adult Patients With Unresectable Advanced, Metastatic Or Recurrent Non-Small Cell Lung Cancer</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>C34.1</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Malignant neoplasm: Upper lobe, bronchus or lung</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Inactivated Hepatitis A Vaccine Adsorbed I.P.</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>SANOFI HEALTHCARE INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>13-MAY-2026</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>For Prevention Of Infection Caused By Hepatitis A Virus In Children In The Age Group Of 12 Months To 15 Years</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>For Prevention Of Infection Caused By Hepatitis A Virus In Children In The Age Group Of 12 Months To 15 Years</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>B95</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Streptococcus and staphylococcus as the cause of diseases classified to other chapters</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Certain infectious and parasitic diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Abiraterone Acetate Tablets Ip</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>MSN Laboratories Private Limited</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>10-JUN-2026</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>For The Treatment Of 1) In Combination With Prednisone For The Treatment Of Patients With Metastatic Castration-Resistant Prostate Cancer Who Have Received Prior Chemotherapy Containing Docetaxel. 2) Indicated For The Treatment Of Metastatic Castration Resistant Prostate Cancer In Adult Men Who Are Asymptomatic Or Mildly Symptomatic After Failure Of Androgen Deprivation Therapy In Whom Chemotherapy Is Not Yet Clinically Indicated, With Prednisone Or Prednisolone.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>1) In Combination With Prednisone For The Treatment Of Patients With Metastatic Castration-Resistant Prostate Cancer</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>C61</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Malignant neoplasm of prostate</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Avibactam 500 Mg+Aztreonam 1500 Mg</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>BDR Pharmaceuticals International Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>10-JUN-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>For The Treatment Of The Following Infections In Adult Patients- Complicated Intra Abdominal Infection, Hospital Acquired Pneumonia, Including Ventilator Associated Pneumonia, Complicated Urinary Tract Infection, Including Pyelonephritis. It Is Also Indicated For The Treatment Of Infections Due To Aerobic Gram Negative Organisms In Adult Patients With Limited Treatment Options. Consideration Should Be Given To Official Guidance On The Appropriate Use Of Antibacterial Agents.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>The</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>O94</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Sequelae of complication of pregnancy, childbirth and the puerperium</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Pregnancy, childbirth and the puerperium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Belumosudil Mesylate-Bulk Drug</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>MSN Organics Private Limited</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>10-JUN-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>REZUROCK is indicated for the treatment of adult and pediatric patients 12 years and older with chronic graft-versus-host disease (chronic GVHD) after failure of at least two prior lines of systemic therapy.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>adult and pediatric patients 12 years and older with chronic graft-versus-host disease (chronic GVHD)</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>T86</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Failure and rejection of transplanted organs and tissues</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Injury, poisoning and certain other consequences of external causes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Bevacizumab</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Dr Reddys Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>10-JUN-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Hepatocellular Carcinoma (Hcc)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Hepatocellular Carcinoma (Hcc)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>C22.0</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Malignant neoplasm: Liver cell carcinoma</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Guselkumab</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>10-JUN-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Ulcerative Colitis,Guselkumab Is Indicated For The Treatment Of Adult Patients With Moderately To Severely Active Crohn?S Disease</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>The Treatment Of Adult Patients With Moderately To Severely Active Crohn?S Disease</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>K50.0</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Crohn disease of small intestine</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Diseases of the digestive system</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Acellular Pertussis Fha Antigen</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>SERUM INSTITUTE OF INDIA PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>05-JUN-2026</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Tripavac is indicated for active booster immunization against tetanus, diphtheria, and pertussis in individuals aged 4 to 65 years.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>active booster immunization against tetanus, diphtheria, and pertussis in individuals aged 4 to 65 years</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Z23</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Need for immunization against single bacterial diseases</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Factors influencing health status and contact with health services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Glycopyrronium+Indacaterol</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Zydus Healthcare Limited</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>01-JUN-2026</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Maintenance Bronchodilator Treatment To Relieve Symptoms And Reduce Exacerbations In Patients With Chronic Obstructive Pulmonary Disease (Copd).</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Maintenance Bronchodilator Treatment To Relieve Symptoms And Reduce Exacerbations In Patients With Chronic Obstructive Pulmonary Disease (Copd)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>J44.9</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Chronic obstructive pulmonary disease, unspecified</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Diseases of the respiratory system</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>